--- a/research/traditional_assets/database/data/argentina/argentina_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_restaurant_dining.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2176815926017831</v>
+        <v>0.2169489570276769</v>
       </c>
       <c r="C2">
-        <v>316.1192368418526</v>
+        <v>314.3202903283847</v>
       </c>
       <c r="D2">
-        <v>315.3822368418526</v>
+        <v>316.7322903283846</v>
       </c>
       <c r="E2">
-        <v>-23.7</v>
+        <v>-20.551</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.149</v>
       </c>
       <c r="G2">
         <v>0.737</v>
@@ -1451,28 +1451,28 @@
         <v>16.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1583947</v>
       </c>
       <c r="N2">
-        <v>16.5</v>
+        <v>16.3416053</v>
       </c>
       <c r="O2">
-        <v>5.774999999999999</v>
+        <v>5.719561855</v>
       </c>
       <c r="P2">
-        <v>10.725</v>
+        <v>10.622043445</v>
       </c>
       <c r="Q2">
-        <v>13.025</v>
+        <v>12.922043445</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2176815926017831</v>
+        <v>0.2188101081087645</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326223</v>
+        <v>0.8500630529351598</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>104.1701521578689</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2169489570276769</v>
+        <v>0.2162163214535707</v>
       </c>
       <c r="C3">
-        <v>314.3202903283847</v>
+        <v>312.5329518252615</v>
       </c>
       <c r="D3">
-        <v>316.7322903283846</v>
+        <v>318.0939518252615</v>
       </c>
       <c r="E3">
-        <v>-20.551</v>
+        <v>-17.402</v>
       </c>
       <c r="F3">
-        <v>3.149</v>
+        <v>6.298</v>
       </c>
       <c r="G3">
         <v>0.737</v>
@@ -1533,28 +1533,28 @@
         <v>16.5</v>
       </c>
       <c r="M3">
-        <v>0.1583947</v>
+        <v>0.3167894</v>
       </c>
       <c r="N3">
-        <v>16.3416053</v>
+        <v>16.1832106</v>
       </c>
       <c r="O3">
-        <v>5.719561855</v>
+        <v>5.664123709999999</v>
       </c>
       <c r="P3">
-        <v>10.622043445</v>
+        <v>10.51908689</v>
       </c>
       <c r="Q3">
-        <v>12.922043445</v>
+        <v>12.81908689</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2188101081087645</v>
+        <v>0.2199616545444598</v>
       </c>
       <c r="T3">
-        <v>0.8500630529351598</v>
+        <v>0.8557210291622388</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>104.1701521578689</v>
+        <v>52.08507607893446</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2162163214535707</v>
+        <v>0.2154836858794644</v>
       </c>
       <c r="C4">
-        <v>312.5329518252615</v>
+        <v>310.7573716906267</v>
       </c>
       <c r="D4">
-        <v>318.0939518252615</v>
+        <v>319.4673716906266</v>
       </c>
       <c r="E4">
-        <v>-17.402</v>
+        <v>-14.253</v>
       </c>
       <c r="F4">
-        <v>6.298</v>
+        <v>9.446999999999999</v>
       </c>
       <c r="G4">
         <v>0.737</v>
@@ -1615,28 +1615,28 @@
         <v>16.5</v>
       </c>
       <c r="M4">
-        <v>0.3167894</v>
+        <v>0.4751840999999999</v>
       </c>
       <c r="N4">
-        <v>16.1832106</v>
+        <v>16.0248159</v>
       </c>
       <c r="O4">
-        <v>5.664123709999999</v>
+        <v>5.608685565</v>
       </c>
       <c r="P4">
-        <v>10.51908689</v>
+        <v>10.416130335</v>
       </c>
       <c r="Q4">
-        <v>12.81908689</v>
+        <v>12.716130335</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2199616545444598</v>
+        <v>0.2211369442056334</v>
       </c>
       <c r="T4">
-        <v>0.8557210291622388</v>
+        <v>0.8614956646929688</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>52.08507607893446</v>
+        <v>34.72338405262298</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2154836858794644</v>
+        <v>0.2147510503053581</v>
       </c>
       <c r="C5">
-        <v>310.7573716906267</v>
+        <v>308.9937028906622</v>
       </c>
       <c r="D5">
-        <v>319.4673716906266</v>
+        <v>320.8527028906622</v>
       </c>
       <c r="E5">
-        <v>-14.253</v>
+        <v>-11.104</v>
       </c>
       <c r="F5">
-        <v>9.446999999999999</v>
+        <v>12.596</v>
       </c>
       <c r="G5">
         <v>0.737</v>
@@ -1697,28 +1697,28 @@
         <v>16.5</v>
       </c>
       <c r="M5">
-        <v>0.4751840999999999</v>
+        <v>0.6335788</v>
       </c>
       <c r="N5">
-        <v>16.0248159</v>
+        <v>15.8664212</v>
       </c>
       <c r="O5">
-        <v>5.608685565</v>
+        <v>5.55324742</v>
       </c>
       <c r="P5">
-        <v>10.416130335</v>
+        <v>10.31317378</v>
       </c>
       <c r="Q5">
-        <v>12.716130335</v>
+        <v>12.61317378</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2211369442056334</v>
+        <v>0.2223367190680814</v>
       </c>
       <c r="T5">
-        <v>0.8614956646929688</v>
+        <v>0.8673906051305892</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.72338405262298</v>
+        <v>26.04253803946723</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2147510503053581</v>
+        <v>0.2140184147312519</v>
       </c>
       <c r="C6">
-        <v>308.9937028906622</v>
+        <v>307.2421010563825</v>
       </c>
       <c r="D6">
-        <v>320.8527028906622</v>
+        <v>322.2501010563825</v>
       </c>
       <c r="E6">
-        <v>-11.104</v>
+        <v>-7.955</v>
       </c>
       <c r="F6">
-        <v>12.596</v>
+        <v>15.745</v>
       </c>
       <c r="G6">
         <v>0.737</v>
@@ -1779,28 +1779,28 @@
         <v>16.5</v>
       </c>
       <c r="M6">
-        <v>0.6335788</v>
+        <v>0.7919734999999999</v>
       </c>
       <c r="N6">
-        <v>15.8664212</v>
+        <v>15.7080265</v>
       </c>
       <c r="O6">
-        <v>5.55324742</v>
+        <v>5.497809275</v>
       </c>
       <c r="P6">
-        <v>10.31317378</v>
+        <v>10.210217225</v>
       </c>
       <c r="Q6">
-        <v>12.61317378</v>
+        <v>12.510217225</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2223367190680814</v>
+        <v>0.2235617523486862</v>
       </c>
       <c r="T6">
-        <v>0.8673906051305892</v>
+        <v>0.8734096495774226</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.04253803946723</v>
+        <v>20.83403043157379</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2140184147312519</v>
+        <v>0.2132857791571456</v>
       </c>
       <c r="C7">
-        <v>307.2421010563825</v>
+        <v>305.5027245419187</v>
       </c>
       <c r="D7">
-        <v>322.2501010563825</v>
+        <v>323.6597245419186</v>
       </c>
       <c r="E7">
-        <v>-7.955</v>
+        <v>-4.806000000000001</v>
       </c>
       <c r="F7">
-        <v>15.745</v>
+        <v>18.894</v>
       </c>
       <c r="G7">
         <v>0.737</v>
@@ -1861,28 +1861,28 @@
         <v>16.5</v>
       </c>
       <c r="M7">
-        <v>0.7919734999999999</v>
+        <v>0.9503681999999999</v>
       </c>
       <c r="N7">
-        <v>15.7080265</v>
+        <v>15.5496318</v>
       </c>
       <c r="O7">
-        <v>5.497809275</v>
+        <v>5.44237113</v>
       </c>
       <c r="P7">
-        <v>10.210217225</v>
+        <v>10.10726067</v>
       </c>
       <c r="Q7">
-        <v>12.510217225</v>
+        <v>12.40726067</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2235617523486862</v>
+        <v>0.2248128501671762</v>
       </c>
       <c r="T7">
-        <v>0.8734096495774226</v>
+        <v>0.8795567587997205</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.83403043157379</v>
+        <v>17.36169202631149</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2132857791571456</v>
+        <v>0.2125531435830394</v>
       </c>
       <c r="C8">
-        <v>305.5027245419187</v>
+        <v>303.7757344843384</v>
       </c>
       <c r="D8">
-        <v>323.6597245419186</v>
+        <v>325.0817344843384</v>
       </c>
       <c r="E8">
-        <v>-4.806000000000001</v>
+        <v>-1.657000000000004</v>
       </c>
       <c r="F8">
-        <v>18.894</v>
+        <v>22.043</v>
       </c>
       <c r="G8">
         <v>0.737</v>
@@ -1943,28 +1943,28 @@
         <v>16.5</v>
       </c>
       <c r="M8">
-        <v>0.9503681999999999</v>
+        <v>1.1087629</v>
       </c>
       <c r="N8">
-        <v>15.5496318</v>
+        <v>15.3912371</v>
       </c>
       <c r="O8">
-        <v>5.44237113</v>
+        <v>5.386932985</v>
       </c>
       <c r="P8">
-        <v>10.10726067</v>
+        <v>10.004304115</v>
       </c>
       <c r="Q8">
-        <v>12.40726067</v>
+        <v>12.304304115</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2248128501671762</v>
+        <v>0.2260908533150961</v>
       </c>
       <c r="T8">
-        <v>0.8795567587997205</v>
+        <v>0.8858360639192721</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.36169202631149</v>
+        <v>14.88145030826699</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2125531435830394</v>
+        <v>0.2118205080089332</v>
       </c>
       <c r="C9">
-        <v>303.7757344843384</v>
+        <v>302.061294865051</v>
       </c>
       <c r="D9">
-        <v>325.0817344843384</v>
+        <v>326.516294865051</v>
       </c>
       <c r="E9">
-        <v>-1.657</v>
+        <v>1.492000000000001</v>
       </c>
       <c r="F9">
-        <v>22.043</v>
+        <v>25.192</v>
       </c>
       <c r="G9">
         <v>0.737</v>
@@ -2025,28 +2025,28 @@
         <v>16.5</v>
       </c>
       <c r="M9">
-        <v>1.1087629</v>
+        <v>1.2671576</v>
       </c>
       <c r="N9">
-        <v>15.3912371</v>
+        <v>15.2328424</v>
       </c>
       <c r="O9">
-        <v>5.386932985</v>
+        <v>5.33149484</v>
       </c>
       <c r="P9">
-        <v>10.004304115</v>
+        <v>9.90134756</v>
       </c>
       <c r="Q9">
-        <v>12.304304115</v>
+        <v>12.20134756</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2260908533150961</v>
+        <v>0.2273966391401448</v>
       </c>
       <c r="T9">
-        <v>0.8858360639192721</v>
+        <v>0.8922518756718575</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.88145030826699</v>
+        <v>13.02126901973361</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2118205080089332</v>
+        <v>0.211175622434827</v>
       </c>
       <c r="C10">
-        <v>302.061294865051</v>
+        <v>300.1855517403324</v>
       </c>
       <c r="D10">
-        <v>326.516294865051</v>
+        <v>327.7895517403324</v>
       </c>
       <c r="E10">
-        <v>1.492000000000001</v>
+        <v>4.640999999999998</v>
       </c>
       <c r="F10">
-        <v>25.192</v>
+        <v>28.341</v>
       </c>
       <c r="G10">
         <v>0.737</v>
@@ -2107,45 +2107,45 @@
         <v>16.5</v>
       </c>
       <c r="M10">
-        <v>1.2671576</v>
+        <v>1.4680638</v>
       </c>
       <c r="N10">
-        <v>15.2328424</v>
+        <v>15.0319362</v>
       </c>
       <c r="O10">
-        <v>5.33149484</v>
+        <v>5.261177669999999</v>
       </c>
       <c r="P10">
-        <v>9.90134756</v>
+        <v>9.770758530000002</v>
       </c>
       <c r="Q10">
-        <v>12.20134756</v>
+        <v>12.07075853</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2273966391401448</v>
+        <v>0.2287311235547549</v>
       </c>
       <c r="T10">
-        <v>0.8922518756718575</v>
+        <v>0.8988086942761481</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.35</v>
       </c>
       <c r="W10">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.02126901973361</v>
+        <v>11.23929355113858</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.211175622434827</v>
+        <v>0.2104527368607207</v>
       </c>
       <c r="C11">
-        <v>300.1855517403324</v>
+        <v>298.4756674380949</v>
       </c>
       <c r="D11">
-        <v>327.7895517403324</v>
+        <v>329.2286674380949</v>
       </c>
       <c r="E11">
-        <v>4.640999999999998</v>
+        <v>7.789999999999996</v>
       </c>
       <c r="F11">
-        <v>28.341</v>
+        <v>31.48999999999999</v>
       </c>
       <c r="G11">
         <v>0.737</v>
@@ -2189,28 +2189,28 @@
         <v>16.5</v>
       </c>
       <c r="M11">
-        <v>1.4680638</v>
+        <v>1.631182</v>
       </c>
       <c r="N11">
-        <v>15.0319362</v>
+        <v>14.868818</v>
       </c>
       <c r="O11">
-        <v>5.261177669999999</v>
+        <v>5.2040863</v>
       </c>
       <c r="P11">
-        <v>9.770758530000002</v>
+        <v>9.664731700000001</v>
       </c>
       <c r="Q11">
-        <v>12.07075853</v>
+        <v>11.9647317</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2287311235547549</v>
+        <v>0.2300952631785786</v>
       </c>
       <c r="T11">
-        <v>0.8988086942761481</v>
+        <v>0.905511219960534</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.23929355113858</v>
+        <v>10.11536419602472</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2104527368607207</v>
+        <v>0.2098514012866145</v>
       </c>
       <c r="C12">
-        <v>298.4756674380949</v>
+        <v>296.5334654794005</v>
       </c>
       <c r="D12">
-        <v>329.2286674380949</v>
+        <v>330.4354654794005</v>
       </c>
       <c r="E12">
-        <v>7.789999999999999</v>
+        <v>10.939</v>
       </c>
       <c r="F12">
-        <v>31.49</v>
+        <v>34.639</v>
       </c>
       <c r="G12">
         <v>0.737</v>
@@ -2271,45 +2271,45 @@
         <v>16.5</v>
       </c>
       <c r="M12">
-        <v>1.631182</v>
+        <v>1.8531865</v>
       </c>
       <c r="N12">
-        <v>14.868818</v>
+        <v>14.6468135</v>
       </c>
       <c r="O12">
-        <v>5.2040863</v>
+        <v>5.126384724999999</v>
       </c>
       <c r="P12">
-        <v>9.664731700000001</v>
+        <v>9.520428775000001</v>
       </c>
       <c r="Q12">
-        <v>11.9647317</v>
+        <v>11.820428775</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2300952631785786</v>
+        <v>0.2314900576254095</v>
       </c>
       <c r="T12">
-        <v>0.905511219960534</v>
+        <v>0.9123643641996252</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.35</v>
       </c>
       <c r="W12">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.11536419602472</v>
+        <v>8.903583098624992</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2098514012866145</v>
+        <v>0.2091395657125082</v>
       </c>
       <c r="C13">
-        <v>296.5334654794005</v>
+        <v>294.8245067715918</v>
       </c>
       <c r="D13">
-        <v>330.4354654794005</v>
+        <v>331.8755067715918</v>
       </c>
       <c r="E13">
-        <v>10.939</v>
+        <v>14.088</v>
       </c>
       <c r="F13">
-        <v>34.639</v>
+        <v>37.788</v>
       </c>
       <c r="G13">
         <v>0.737</v>
@@ -2353,28 +2353,28 @@
         <v>16.5</v>
       </c>
       <c r="M13">
-        <v>1.8531865</v>
+        <v>2.021658</v>
       </c>
       <c r="N13">
-        <v>14.6468135</v>
+        <v>14.478342</v>
       </c>
       <c r="O13">
-        <v>5.126384724999999</v>
+        <v>5.067419699999999</v>
       </c>
       <c r="P13">
-        <v>9.520428775000001</v>
+        <v>9.410922299999999</v>
       </c>
       <c r="Q13">
-        <v>11.820428775</v>
+        <v>11.7109223</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2314900576254095</v>
+        <v>0.2329165519460321</v>
       </c>
       <c r="T13">
-        <v>0.9123643641996252</v>
+        <v>0.9193732617168775</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.903583098624992</v>
+        <v>8.16161784040624</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2091395657125082</v>
+        <v>0.2084953301384019</v>
       </c>
       <c r="C14">
-        <v>294.8245067715918</v>
+        <v>292.9896563999488</v>
       </c>
       <c r="D14">
-        <v>331.8755067715918</v>
+        <v>333.1896563999488</v>
       </c>
       <c r="E14">
-        <v>14.088</v>
+        <v>17.237</v>
       </c>
       <c r="F14">
-        <v>37.788</v>
+        <v>40.937</v>
       </c>
       <c r="G14">
         <v>0.737</v>
@@ -2435,45 +2435,45 @@
         <v>16.5</v>
       </c>
       <c r="M14">
-        <v>2.021658</v>
+        <v>2.2228791</v>
       </c>
       <c r="N14">
-        <v>14.478342</v>
+        <v>14.2771209</v>
       </c>
       <c r="O14">
-        <v>5.067419699999999</v>
+        <v>4.996992315</v>
       </c>
       <c r="P14">
-        <v>9.410922299999999</v>
+        <v>9.280128585</v>
       </c>
       <c r="Q14">
-        <v>11.7109223</v>
+        <v>11.580128585</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2329165519460321</v>
+        <v>0.2343758392395425</v>
       </c>
       <c r="T14">
-        <v>0.9193732617168775</v>
+        <v>0.9265432833149861</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.35</v>
       </c>
       <c r="W14">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.16161784040624</v>
+        <v>7.422805855703083</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2084953301384019</v>
+        <v>0.2077886945642957</v>
       </c>
       <c r="C15">
-        <v>292.9896563999488</v>
+        <v>291.2941137833157</v>
       </c>
       <c r="D15">
-        <v>333.1896563999488</v>
+        <v>334.6431137833156</v>
       </c>
       <c r="E15">
-        <v>17.237</v>
+        <v>20.386</v>
       </c>
       <c r="F15">
-        <v>40.937</v>
+        <v>44.086</v>
       </c>
       <c r="G15">
         <v>0.737</v>
@@ -2517,28 +2517,28 @@
         <v>16.5</v>
       </c>
       <c r="M15">
-        <v>2.2228791</v>
+        <v>2.3938698</v>
       </c>
       <c r="N15">
-        <v>14.2771209</v>
+        <v>14.1061302</v>
       </c>
       <c r="O15">
-        <v>4.996992315</v>
+        <v>4.937145569999999</v>
       </c>
       <c r="P15">
-        <v>9.280128585</v>
+        <v>9.168984630000001</v>
       </c>
       <c r="Q15">
-        <v>11.580128585</v>
+        <v>11.46898463</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2343758392395425</v>
+        <v>0.2358690634468555</v>
       </c>
       <c r="T15">
-        <v>0.9265432833149861</v>
+        <v>0.9338800496014231</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.422805855703083</v>
+        <v>6.892605437438577</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2077886945642957</v>
+        <v>0.2070820589901895</v>
       </c>
       <c r="C16">
-        <v>291.2941137833157</v>
+        <v>289.6113074214026</v>
       </c>
       <c r="D16">
-        <v>334.6431137833156</v>
+        <v>336.1093074214025</v>
       </c>
       <c r="E16">
-        <v>20.386</v>
+        <v>23.53500000000001</v>
       </c>
       <c r="F16">
-        <v>44.086</v>
+        <v>47.23500000000001</v>
       </c>
       <c r="G16">
         <v>0.737</v>
@@ -2599,28 +2599,28 @@
         <v>16.5</v>
       </c>
       <c r="M16">
-        <v>2.3938698</v>
+        <v>2.5648605</v>
       </c>
       <c r="N16">
-        <v>14.1061302</v>
+        <v>13.9351395</v>
       </c>
       <c r="O16">
-        <v>4.937145569999999</v>
+        <v>4.877298825</v>
       </c>
       <c r="P16">
-        <v>9.168984630000001</v>
+        <v>9.057840675000001</v>
       </c>
       <c r="Q16">
-        <v>11.46898463</v>
+        <v>11.357840675</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2358690634468555</v>
+        <v>0.2373974223413994</v>
       </c>
       <c r="T16">
-        <v>0.9338800496014231</v>
+        <v>0.9413894456828349</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.892605437438577</v>
+        <v>6.433098408276004</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2070820589901895</v>
+        <v>0.2064794234160833</v>
       </c>
       <c r="C17">
-        <v>289.6113074214026</v>
+        <v>287.7229008510654</v>
       </c>
       <c r="D17">
-        <v>336.1093074214025</v>
+        <v>337.3699008510654</v>
       </c>
       <c r="E17">
-        <v>23.53499999999999</v>
+        <v>26.684</v>
       </c>
       <c r="F17">
-        <v>47.23499999999999</v>
+        <v>50.384</v>
       </c>
       <c r="G17">
         <v>0.737</v>
@@ -2681,45 +2681,45 @@
         <v>16.5</v>
       </c>
       <c r="M17">
-        <v>2.5648605</v>
+        <v>2.7862352</v>
       </c>
       <c r="N17">
-        <v>13.9351395</v>
+        <v>13.7137648</v>
       </c>
       <c r="O17">
-        <v>4.877298825</v>
+        <v>4.799817679999999</v>
       </c>
       <c r="P17">
-        <v>9.057840675000001</v>
+        <v>8.91394712</v>
       </c>
       <c r="Q17">
-        <v>11.357840675</v>
+        <v>11.21394712</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2373974223413994</v>
+        <v>0.2389621707334325</v>
       </c>
       <c r="T17">
-        <v>0.9413894456828349</v>
+        <v>0.9490776369090422</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.35</v>
       </c>
       <c r="W17">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.433098408276007</v>
+        <v>5.921969545141056</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2064794234160833</v>
+        <v>0.205779287841977</v>
       </c>
       <c r="C18">
-        <v>287.7229008510654</v>
+        <v>286.0503711642216</v>
       </c>
       <c r="D18">
-        <v>337.3699008510654</v>
+        <v>338.8463711642216</v>
       </c>
       <c r="E18">
-        <v>26.684</v>
+        <v>29.833</v>
       </c>
       <c r="F18">
-        <v>50.384</v>
+        <v>53.533</v>
       </c>
       <c r="G18">
         <v>0.737</v>
@@ -2763,28 +2763,28 @@
         <v>16.5</v>
       </c>
       <c r="M18">
-        <v>2.7862352</v>
+        <v>2.9603749</v>
       </c>
       <c r="N18">
-        <v>13.7137648</v>
+        <v>13.5396251</v>
       </c>
       <c r="O18">
-        <v>4.799817679999999</v>
+        <v>4.738868785</v>
       </c>
       <c r="P18">
-        <v>8.91394712</v>
+        <v>8.800756315000001</v>
       </c>
       <c r="Q18">
-        <v>11.21394712</v>
+        <v>11.100756315</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2389621707334325</v>
+        <v>0.2405646239059964</v>
       </c>
       <c r="T18">
-        <v>0.9490776369090422</v>
+        <v>0.9569510857551583</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.921969545141056</v>
+        <v>5.573618395426877</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.205779287841977</v>
+        <v>0.2050791522678707</v>
       </c>
       <c r="C19">
-        <v>286.0503711642216</v>
+        <v>284.3908215739646</v>
       </c>
       <c r="D19">
-        <v>338.8463711642216</v>
+        <v>340.3358215739646</v>
       </c>
       <c r="E19">
-        <v>29.833</v>
+        <v>32.982</v>
       </c>
       <c r="F19">
-        <v>53.533</v>
+        <v>56.682</v>
       </c>
       <c r="G19">
         <v>0.737</v>
@@ -2845,28 +2845,28 @@
         <v>16.5</v>
       </c>
       <c r="M19">
-        <v>2.9603749</v>
+        <v>3.1345146</v>
       </c>
       <c r="N19">
-        <v>13.5396251</v>
+        <v>13.3654854</v>
       </c>
       <c r="O19">
-        <v>4.738868785</v>
+        <v>4.67791989</v>
       </c>
       <c r="P19">
-        <v>8.800756315000001</v>
+        <v>8.687565510000001</v>
       </c>
       <c r="Q19">
-        <v>11.100756315</v>
+        <v>10.98756551</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2405646239059964</v>
+        <v>0.2422061613022814</v>
       </c>
       <c r="T19">
-        <v>0.9569510857551583</v>
+        <v>0.9650165699389842</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.573618395426877</v>
+        <v>5.263972929014272</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2050791522678708</v>
+        <v>0.2043790166937645</v>
       </c>
       <c r="C20">
-        <v>284.3908215739645</v>
+        <v>282.7444240039364</v>
       </c>
       <c r="D20">
-        <v>340.3358215739645</v>
+        <v>341.8384240039364</v>
       </c>
       <c r="E20">
-        <v>32.982</v>
+        <v>36.131</v>
       </c>
       <c r="F20">
-        <v>56.682</v>
+        <v>59.831</v>
       </c>
       <c r="G20">
         <v>0.737</v>
@@ -2927,28 +2927,28 @@
         <v>16.5</v>
       </c>
       <c r="M20">
-        <v>3.1345146</v>
+        <v>3.3086543</v>
       </c>
       <c r="N20">
-        <v>13.3654854</v>
+        <v>13.1913457</v>
       </c>
       <c r="O20">
-        <v>4.67791989</v>
+        <v>4.616970994999999</v>
       </c>
       <c r="P20">
-        <v>8.687565510000001</v>
+        <v>8.574374705</v>
       </c>
       <c r="Q20">
-        <v>10.98756551</v>
+        <v>10.874374705</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2422061613022814</v>
+        <v>0.2438882304861291</v>
       </c>
       <c r="T20">
-        <v>0.9650165699389842</v>
+        <v>0.9732812018804359</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.263972929014272</v>
+        <v>4.986921722224047</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2043790166937645</v>
+        <v>0.2036788811196583</v>
       </c>
       <c r="C21">
-        <v>282.7444240039364</v>
+        <v>281.1113534274554</v>
       </c>
       <c r="D21">
-        <v>341.8384240039364</v>
+        <v>343.3543534274554</v>
       </c>
       <c r="E21">
-        <v>36.131</v>
+        <v>39.28</v>
       </c>
       <c r="F21">
-        <v>59.831</v>
+        <v>62.98</v>
       </c>
       <c r="G21">
         <v>0.737</v>
@@ -3009,28 +3009,28 @@
         <v>16.5</v>
       </c>
       <c r="M21">
-        <v>3.3086543</v>
+        <v>3.482794</v>
       </c>
       <c r="N21">
-        <v>13.1913457</v>
+        <v>13.017206</v>
       </c>
       <c r="O21">
-        <v>4.616970994999999</v>
+        <v>4.5560221</v>
       </c>
       <c r="P21">
-        <v>8.574374705</v>
+        <v>8.4611839</v>
       </c>
       <c r="Q21">
-        <v>10.874374705</v>
+        <v>10.7611839</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2438882304861291</v>
+        <v>0.2456123513995729</v>
       </c>
       <c r="T21">
-        <v>0.9732812018804359</v>
+        <v>0.9817524496204235</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.986921722224047</v>
+        <v>4.737575636112845</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2036788811196583</v>
+        <v>0.2029787455455521</v>
       </c>
       <c r="C22">
-        <v>281.1113534274554</v>
+        <v>279.4917879354381</v>
       </c>
       <c r="D22">
-        <v>343.3543534274554</v>
+        <v>344.8837879354381</v>
       </c>
       <c r="E22">
-        <v>39.28</v>
+        <v>42.429</v>
       </c>
       <c r="F22">
-        <v>62.98</v>
+        <v>66.129</v>
       </c>
       <c r="G22">
         <v>0.737</v>
@@ -3091,28 +3091,28 @@
         <v>16.5</v>
       </c>
       <c r="M22">
-        <v>3.482794</v>
+        <v>3.656933700000001</v>
       </c>
       <c r="N22">
-        <v>13.017206</v>
+        <v>12.8430663</v>
       </c>
       <c r="O22">
-        <v>4.5560221</v>
+        <v>4.495073205</v>
       </c>
       <c r="P22">
-        <v>8.4611839</v>
+        <v>8.347993095</v>
       </c>
       <c r="Q22">
-        <v>10.7611839</v>
+        <v>10.647993095</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2456123513995729</v>
+        <v>0.2473801209437368</v>
       </c>
       <c r="T22">
-        <v>0.9817524496204235</v>
+        <v>0.9904381593285122</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.737575636112845</v>
+        <v>4.511976796297947</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2029787455455521</v>
+        <v>0.2026361099714458</v>
       </c>
       <c r="C23">
-        <v>279.4917879354382</v>
+        <v>277.0962461454176</v>
       </c>
       <c r="D23">
-        <v>344.8837879354381</v>
+        <v>345.6372461454175</v>
       </c>
       <c r="E23">
-        <v>42.42899999999999</v>
+        <v>45.57799999999999</v>
       </c>
       <c r="F23">
-        <v>66.12899999999999</v>
+        <v>69.27799999999999</v>
       </c>
       <c r="G23">
         <v>0.737</v>
@@ -3173,45 +3173,45 @@
         <v>16.5</v>
       </c>
       <c r="M23">
-        <v>3.6569337</v>
+        <v>4.0042684</v>
       </c>
       <c r="N23">
-        <v>12.8430663</v>
+        <v>12.4957316</v>
       </c>
       <c r="O23">
-        <v>4.495073205</v>
+        <v>4.37350606</v>
       </c>
       <c r="P23">
-        <v>8.347993095</v>
+        <v>8.122225539999999</v>
       </c>
       <c r="Q23">
-        <v>10.647993095</v>
+        <v>10.42222554</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2473801209437368</v>
+        <v>0.24919321791211</v>
       </c>
       <c r="T23">
-        <v>0.9904381593285122</v>
+        <v>0.9993465795419364</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.35</v>
       </c>
       <c r="W23">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.511976796297947</v>
+        <v>4.120602904640458</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2026361099714458</v>
+        <v>0.2024754743973395</v>
       </c>
       <c r="C24">
-        <v>277.0962461454176</v>
+        <v>274.3016196533366</v>
       </c>
       <c r="D24">
-        <v>345.6372461454175</v>
+        <v>345.9916196533366</v>
       </c>
       <c r="E24">
-        <v>45.57799999999999</v>
+        <v>48.72699999999999</v>
       </c>
       <c r="F24">
-        <v>69.27799999999999</v>
+        <v>72.42699999999999</v>
       </c>
       <c r="G24">
         <v>0.737</v>
@@ -3255,45 +3255,45 @@
         <v>16.5</v>
       </c>
       <c r="M24">
-        <v>4.0042684</v>
+        <v>4.439775099999999</v>
       </c>
       <c r="N24">
-        <v>12.4957316</v>
+        <v>12.0602249</v>
       </c>
       <c r="O24">
-        <v>4.37350606</v>
+        <v>4.221078715</v>
       </c>
       <c r="P24">
-        <v>8.122225539999999</v>
+        <v>7.839146185000001</v>
       </c>
       <c r="Q24">
-        <v>10.42222554</v>
+        <v>10.139146185</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.24919321791211</v>
+        <v>0.2510534083082332</v>
       </c>
       <c r="T24">
-        <v>0.9993465795419364</v>
+        <v>1.008486387293372</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.120602904640458</v>
+        <v>3.716404463820702</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2024754743973395</v>
+        <v>0.2018143388232333</v>
       </c>
       <c r="C25">
-        <v>274.3016196533366</v>
+        <v>272.6188141699486</v>
       </c>
       <c r="D25">
-        <v>345.9916196533366</v>
+        <v>347.4578141699485</v>
       </c>
       <c r="E25">
-        <v>48.72699999999999</v>
+        <v>51.87599999999999</v>
       </c>
       <c r="F25">
-        <v>72.42699999999999</v>
+        <v>75.57599999999999</v>
       </c>
       <c r="G25">
         <v>0.737</v>
@@ -3337,28 +3337,28 @@
         <v>16.5</v>
       </c>
       <c r="M25">
-        <v>4.439775099999999</v>
+        <v>4.632808799999999</v>
       </c>
       <c r="N25">
-        <v>12.0602249</v>
+        <v>11.8671912</v>
       </c>
       <c r="O25">
-        <v>4.221078715</v>
+        <v>4.15351692</v>
       </c>
       <c r="P25">
-        <v>7.839146185000001</v>
+        <v>7.71367428</v>
       </c>
       <c r="Q25">
-        <v>10.139146185</v>
+        <v>10.01367428</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2510534083082332</v>
+        <v>0.2529625510832017</v>
       </c>
       <c r="T25">
-        <v>1.008486387293372</v>
+        <v>1.017866716301424</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.716404463820702</v>
+        <v>3.561554277828173</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2018143388232333</v>
+        <v>0.2016082032491271</v>
       </c>
       <c r="C26">
-        <v>272.6188141699486</v>
+        <v>269.9295038044352</v>
       </c>
       <c r="D26">
-        <v>347.4578141699485</v>
+        <v>347.9175038044352</v>
       </c>
       <c r="E26">
-        <v>51.87599999999999</v>
+        <v>55.02499999999999</v>
       </c>
       <c r="F26">
-        <v>75.57599999999999</v>
+        <v>78.72499999999999</v>
       </c>
       <c r="G26">
         <v>0.737</v>
@@ -3419,45 +3419,45 @@
         <v>16.5</v>
       </c>
       <c r="M26">
-        <v>4.632808799999999</v>
+        <v>5.0462725</v>
       </c>
       <c r="N26">
-        <v>11.8671912</v>
+        <v>11.4537275</v>
       </c>
       <c r="O26">
-        <v>4.15351692</v>
+        <v>4.008804625</v>
       </c>
       <c r="P26">
-        <v>7.71367428</v>
+        <v>7.444922875</v>
       </c>
       <c r="Q26">
-        <v>10.01367428</v>
+        <v>9.744922874999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2529625510832017</v>
+        <v>0.2549226043321695</v>
       </c>
       <c r="T26">
-        <v>1.017866716301424</v>
+        <v>1.027497187416357</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.35</v>
       </c>
       <c r="W26">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.561554277828173</v>
+        <v>3.26974018941704</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2016082032491271</v>
+        <v>0.2009652676750208</v>
       </c>
       <c r="C27">
-        <v>269.9295038044352</v>
+        <v>268.222118563987</v>
       </c>
       <c r="D27">
-        <v>347.9175038044352</v>
+        <v>349.359118563987</v>
       </c>
       <c r="E27">
-        <v>55.02499999999999</v>
+        <v>58.17399999999999</v>
       </c>
       <c r="F27">
-        <v>78.72499999999999</v>
+        <v>81.874</v>
       </c>
       <c r="G27">
         <v>0.737</v>
@@ -3501,28 +3501,28 @@
         <v>16.5</v>
       </c>
       <c r="M27">
-        <v>5.0462725</v>
+        <v>5.2481234</v>
       </c>
       <c r="N27">
-        <v>11.4537275</v>
+        <v>11.2518766</v>
       </c>
       <c r="O27">
-        <v>4.008804625</v>
+        <v>3.938156809999999</v>
       </c>
       <c r="P27">
-        <v>7.444922875</v>
+        <v>7.31371979</v>
       </c>
       <c r="Q27">
-        <v>9.744922874999999</v>
+        <v>9.613719789999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2549226043321695</v>
+        <v>0.2569356319932714</v>
       </c>
       <c r="T27">
-        <v>1.027497187416357</v>
+        <v>1.037387941534397</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.26974018941704</v>
+        <v>3.143980951362539</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2009652676750208</v>
+        <v>0.2003223321009146</v>
       </c>
       <c r="C28">
-        <v>268.222118563987</v>
+        <v>266.5267298472835</v>
       </c>
       <c r="D28">
-        <v>349.359118563987</v>
+        <v>350.8127298472835</v>
       </c>
       <c r="E28">
-        <v>58.17399999999999</v>
+        <v>61.32299999999999</v>
       </c>
       <c r="F28">
-        <v>81.874</v>
+        <v>85.023</v>
       </c>
       <c r="G28">
         <v>0.737</v>
@@ -3583,28 +3583,28 @@
         <v>16.5</v>
       </c>
       <c r="M28">
-        <v>5.2481234</v>
+        <v>5.4499743</v>
       </c>
       <c r="N28">
-        <v>11.2518766</v>
+        <v>11.0500257</v>
       </c>
       <c r="O28">
-        <v>3.938156809999999</v>
+        <v>3.867508994999999</v>
       </c>
       <c r="P28">
-        <v>7.31371979</v>
+        <v>7.182516704999999</v>
       </c>
       <c r="Q28">
-        <v>9.613719789999999</v>
+        <v>9.482516704999998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2569356319932714</v>
+        <v>0.2590038110971433</v>
       </c>
       <c r="T28">
-        <v>1.037387941534397</v>
+        <v>1.047549675217315</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.143980951362539</v>
+        <v>3.027537212423185</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2003223321009146</v>
+        <v>0.2010989965268084</v>
       </c>
       <c r="C29">
-        <v>266.5267298472835</v>
+        <v>261.6232834341283</v>
       </c>
       <c r="D29">
-        <v>350.8127298472835</v>
+        <v>349.0582834341283</v>
       </c>
       <c r="E29">
-        <v>61.32299999999999</v>
+        <v>64.47199999999999</v>
       </c>
       <c r="F29">
-        <v>85.023</v>
+        <v>88.172</v>
       </c>
       <c r="G29">
         <v>0.737</v>
@@ -3665,45 +3665,45 @@
         <v>16.5</v>
       </c>
       <c r="M29">
-        <v>5.4499743</v>
+        <v>6.3395668</v>
       </c>
       <c r="N29">
-        <v>11.0500257</v>
+        <v>10.1604332</v>
       </c>
       <c r="O29">
-        <v>3.867508994999999</v>
+        <v>3.55615162</v>
       </c>
       <c r="P29">
-        <v>7.182516704999999</v>
+        <v>6.60428158</v>
       </c>
       <c r="Q29">
-        <v>9.482516704999998</v>
+        <v>8.904281579999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2590038110971433</v>
+        <v>0.2611294396205672</v>
       </c>
       <c r="T29">
-        <v>1.047549675217315</v>
+        <v>1.057993679280313</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.027537212423185</v>
+        <v>2.602701496890923</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2010989965268084</v>
+        <v>0.2005067609527021</v>
       </c>
       <c r="C30">
-        <v>261.6232834341283</v>
+        <v>259.810519365985</v>
       </c>
       <c r="D30">
-        <v>349.0582834341283</v>
+        <v>350.3945193659849</v>
       </c>
       <c r="E30">
-        <v>64.47199999999999</v>
+        <v>67.621</v>
       </c>
       <c r="F30">
-        <v>88.172</v>
+        <v>91.321</v>
       </c>
       <c r="G30">
         <v>0.737</v>
@@ -3747,28 +3747,28 @@
         <v>16.5</v>
       </c>
       <c r="M30">
-        <v>6.3395668</v>
+        <v>6.5659799</v>
       </c>
       <c r="N30">
-        <v>10.1604332</v>
+        <v>9.9340201</v>
       </c>
       <c r="O30">
-        <v>3.55615162</v>
+        <v>3.476907035</v>
       </c>
       <c r="P30">
-        <v>6.60428158</v>
+        <v>6.457113065</v>
       </c>
       <c r="Q30">
-        <v>8.904281579999999</v>
+        <v>8.757113064999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2611294396205672</v>
+        <v>0.2633149450038058</v>
       </c>
       <c r="T30">
-        <v>1.057993679280313</v>
+        <v>1.068731880640861</v>
       </c>
       <c r="U30">
         <v>0.07190000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.602701496890923</v>
+        <v>2.512953169411926</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2005067609527021</v>
+        <v>0.2006750253785959</v>
       </c>
       <c r="C31">
-        <v>259.810519365985</v>
+        <v>256.2808322119825</v>
       </c>
       <c r="D31">
-        <v>350.3945193659849</v>
+        <v>350.0138322119824</v>
       </c>
       <c r="E31">
-        <v>67.62099999999998</v>
+        <v>70.76999999999998</v>
       </c>
       <c r="F31">
-        <v>91.32099999999998</v>
+        <v>94.46999999999998</v>
       </c>
       <c r="G31">
         <v>0.737</v>
@@ -3829,45 +3829,45 @@
         <v>16.5</v>
       </c>
       <c r="M31">
-        <v>6.565979899999999</v>
+        <v>7.160825999999999</v>
       </c>
       <c r="N31">
-        <v>9.934020100000001</v>
+        <v>9.339174</v>
       </c>
       <c r="O31">
-        <v>3.476907035</v>
+        <v>3.2687109</v>
       </c>
       <c r="P31">
-        <v>6.457113065000001</v>
+        <v>6.0704631</v>
       </c>
       <c r="Q31">
-        <v>8.757113065</v>
+        <v>8.370463099999998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2633149450038058</v>
+        <v>0.2655628933979941</v>
       </c>
       <c r="T31">
-        <v>1.068731880640861</v>
+        <v>1.079776887754567</v>
       </c>
       <c r="U31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.35</v>
       </c>
       <c r="W31">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.512953169411926</v>
+        <v>2.304203453623925</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2006750253785959</v>
+        <v>0.2001081398044896</v>
       </c>
       <c r="C32">
-        <v>256.2808322119825</v>
+        <v>254.4176865581629</v>
       </c>
       <c r="D32">
-        <v>350.0138322119824</v>
+        <v>351.2996865581629</v>
       </c>
       <c r="E32">
-        <v>70.76999999999998</v>
+        <v>73.91899999999998</v>
       </c>
       <c r="F32">
-        <v>94.46999999999998</v>
+        <v>97.61899999999999</v>
       </c>
       <c r="G32">
         <v>0.737</v>
@@ -3911,28 +3911,28 @@
         <v>16.5</v>
       </c>
       <c r="M32">
-        <v>7.160825999999999</v>
+        <v>7.3995202</v>
       </c>
       <c r="N32">
-        <v>9.339174</v>
+        <v>9.1004798</v>
       </c>
       <c r="O32">
-        <v>3.2687109</v>
+        <v>3.18516793</v>
       </c>
       <c r="P32">
-        <v>6.0704631</v>
+        <v>5.91531187</v>
       </c>
       <c r="Q32">
-        <v>8.370463099999998</v>
+        <v>8.215311869999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2655628933979941</v>
+        <v>0.2678759997166517</v>
       </c>
       <c r="T32">
-        <v>1.079776887754567</v>
+        <v>1.091142040002004</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.304203453623925</v>
+        <v>2.229874309958638</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2001081398044896</v>
+        <v>0.1995412542303834</v>
       </c>
       <c r="C33">
-        <v>254.4176865581629</v>
+        <v>252.5640234896507</v>
       </c>
       <c r="D33">
-        <v>351.2996865581629</v>
+        <v>352.5950234896507</v>
       </c>
       <c r="E33">
-        <v>73.91899999999998</v>
+        <v>77.068</v>
       </c>
       <c r="F33">
-        <v>97.61899999999999</v>
+        <v>100.768</v>
       </c>
       <c r="G33">
         <v>0.737</v>
@@ -3993,28 +3993,28 @@
         <v>16.5</v>
       </c>
       <c r="M33">
-        <v>7.3995202</v>
+        <v>7.638214400000001</v>
       </c>
       <c r="N33">
-        <v>9.1004798</v>
+        <v>8.861785599999999</v>
       </c>
       <c r="O33">
-        <v>3.18516793</v>
+        <v>3.10162496</v>
       </c>
       <c r="P33">
-        <v>5.91531187</v>
+        <v>5.76016064</v>
       </c>
       <c r="Q33">
-        <v>8.215311869999999</v>
+        <v>8.060160639999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2678759997166517</v>
+        <v>0.2702571385740932</v>
       </c>
       <c r="T33">
-        <v>1.091142040002004</v>
+        <v>1.102841461433189</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.229874309958638</v>
+        <v>2.16019073777243</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1995412542303834</v>
+        <v>0.1989743686562772</v>
       </c>
       <c r="C34">
-        <v>252.5640234896507</v>
+        <v>250.7199482892199</v>
       </c>
       <c r="D34">
-        <v>352.5950234896507</v>
+        <v>353.8999482892199</v>
       </c>
       <c r="E34">
-        <v>77.068</v>
+        <v>80.217</v>
       </c>
       <c r="F34">
-        <v>100.768</v>
+        <v>103.917</v>
       </c>
       <c r="G34">
         <v>0.737</v>
@@ -4075,28 +4075,28 @@
         <v>16.5</v>
       </c>
       <c r="M34">
-        <v>7.638214400000001</v>
+        <v>7.876908600000001</v>
       </c>
       <c r="N34">
-        <v>8.861785599999999</v>
+        <v>8.6230914</v>
       </c>
       <c r="O34">
-        <v>3.10162496</v>
+        <v>3.01808199</v>
       </c>
       <c r="P34">
-        <v>5.76016064</v>
+        <v>5.60500941</v>
       </c>
       <c r="Q34">
-        <v>8.060160639999999</v>
+        <v>7.905009409999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2702571385740932</v>
+        <v>0.2727093562033988</v>
       </c>
       <c r="T34">
-        <v>1.102841461433189</v>
+        <v>1.114890119325007</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.16019073777243</v>
+        <v>2.094730412385386</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1989743686562772</v>
+        <v>0.1984074830821709</v>
       </c>
       <c r="C35">
-        <v>250.7199482892199</v>
+        <v>248.8855678040053</v>
       </c>
       <c r="D35">
-        <v>353.8999482892199</v>
+        <v>355.2145678040052</v>
       </c>
       <c r="E35">
-        <v>80.217</v>
+        <v>83.366</v>
       </c>
       <c r="F35">
-        <v>103.917</v>
+        <v>107.066</v>
       </c>
       <c r="G35">
         <v>0.737</v>
@@ -4157,28 +4157,28 @@
         <v>16.5</v>
       </c>
       <c r="M35">
-        <v>7.876908600000001</v>
+        <v>8.115602800000001</v>
       </c>
       <c r="N35">
-        <v>8.6230914</v>
+        <v>8.384397199999999</v>
       </c>
       <c r="O35">
-        <v>3.01808199</v>
+        <v>2.934539019999999</v>
       </c>
       <c r="P35">
-        <v>5.60500941</v>
+        <v>5.44985818</v>
       </c>
       <c r="Q35">
-        <v>7.905009409999999</v>
+        <v>7.749858179999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2727093562033988</v>
+        <v>0.2752358834578347</v>
       </c>
       <c r="T35">
-        <v>1.114890119325007</v>
+        <v>1.127303888062031</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.094730412385386</v>
+        <v>2.033120694374052</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1984074830821709</v>
+        <v>0.2010710975080647</v>
       </c>
       <c r="C36">
-        <v>248.8855678040053</v>
+        <v>239.6430020195474</v>
       </c>
       <c r="D36">
-        <v>355.2145678040052</v>
+        <v>349.1210020195474</v>
       </c>
       <c r="E36">
-        <v>83.366</v>
+        <v>86.515</v>
       </c>
       <c r="F36">
-        <v>107.066</v>
+        <v>110.215</v>
       </c>
       <c r="G36">
         <v>0.737</v>
@@ -4239,45 +4239,45 @@
         <v>16.5</v>
       </c>
       <c r="M36">
-        <v>8.115602800000001</v>
+        <v>9.91935</v>
       </c>
       <c r="N36">
-        <v>8.384397199999999</v>
+        <v>6.58065</v>
       </c>
       <c r="O36">
-        <v>2.934539019999999</v>
+        <v>2.3032275</v>
       </c>
       <c r="P36">
-        <v>5.44985818</v>
+        <v>4.2774225</v>
       </c>
       <c r="Q36">
-        <v>7.749858179999999</v>
+        <v>6.577422499999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2752358834578347</v>
+        <v>0.2778401500124072</v>
       </c>
       <c r="T36">
-        <v>1.127303888062031</v>
+        <v>1.14009961891404</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
         <v>0.35</v>
       </c>
       <c r="W36">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.033120694374052</v>
+        <v>1.66341544556851</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2010710975080647</v>
+        <v>0.2005965119339584</v>
       </c>
       <c r="C37">
-        <v>239.6430020195474</v>
+        <v>237.5643607059672</v>
       </c>
       <c r="D37">
-        <v>349.1210020195474</v>
+        <v>350.1913607059672</v>
       </c>
       <c r="E37">
-        <v>86.515</v>
+        <v>89.664</v>
       </c>
       <c r="F37">
-        <v>110.215</v>
+        <v>113.364</v>
       </c>
       <c r="G37">
         <v>0.737</v>
@@ -4321,28 +4321,28 @@
         <v>16.5</v>
       </c>
       <c r="M37">
-        <v>9.91935</v>
+        <v>10.20276</v>
       </c>
       <c r="N37">
-        <v>6.58065</v>
+        <v>6.29724</v>
       </c>
       <c r="O37">
-        <v>2.3032275</v>
+        <v>2.204034</v>
       </c>
       <c r="P37">
-        <v>4.2774225</v>
+        <v>4.093206</v>
       </c>
       <c r="Q37">
-        <v>6.577422499999999</v>
+        <v>6.393205999999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2778401500124072</v>
+        <v>0.2805257998968101</v>
       </c>
       <c r="T37">
-        <v>1.14009961891404</v>
+        <v>1.153295216355175</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.66341544556851</v>
+        <v>1.617209460969385</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2005965119339584</v>
+        <v>0.2001219263598522</v>
       </c>
       <c r="C38">
-        <v>237.5643607059671</v>
+        <v>235.4923027315621</v>
       </c>
       <c r="D38">
-        <v>350.1913607059671</v>
+        <v>351.268302731562</v>
       </c>
       <c r="E38">
-        <v>89.66399999999999</v>
+        <v>92.81299999999999</v>
       </c>
       <c r="F38">
-        <v>113.364</v>
+        <v>116.513</v>
       </c>
       <c r="G38">
         <v>0.737</v>
@@ -4403,28 +4403,28 @@
         <v>16.5</v>
       </c>
       <c r="M38">
-        <v>10.20276</v>
+        <v>10.48617</v>
       </c>
       <c r="N38">
-        <v>6.29724</v>
+        <v>6.01383</v>
       </c>
       <c r="O38">
-        <v>2.204034</v>
+        <v>2.1048405</v>
       </c>
       <c r="P38">
-        <v>4.093206</v>
+        <v>3.908989500000001</v>
       </c>
       <c r="Q38">
-        <v>6.393205999999999</v>
+        <v>6.208989499999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2805257998968101</v>
+        <v>0.2832967085077019</v>
       </c>
       <c r="T38">
-        <v>1.153295216355175</v>
+        <v>1.166909721651584</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.617209460969385</v>
+        <v>1.573501097159401</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2001219263598522</v>
+        <v>0.1996473407857459</v>
       </c>
       <c r="C39">
-        <v>235.4923027315621</v>
+        <v>233.4268890208392</v>
       </c>
       <c r="D39">
-        <v>351.268302731562</v>
+        <v>352.3518890208392</v>
       </c>
       <c r="E39">
-        <v>92.81299999999999</v>
+        <v>95.96199999999999</v>
       </c>
       <c r="F39">
-        <v>116.513</v>
+        <v>119.662</v>
       </c>
       <c r="G39">
         <v>0.737</v>
@@ -4485,28 +4485,28 @@
         <v>16.5</v>
       </c>
       <c r="M39">
-        <v>10.48617</v>
+        <v>10.76958</v>
       </c>
       <c r="N39">
-        <v>6.01383</v>
+        <v>5.730420000000001</v>
       </c>
       <c r="O39">
-        <v>2.1048405</v>
+        <v>2.005647</v>
       </c>
       <c r="P39">
-        <v>3.908989500000001</v>
+        <v>3.724773</v>
       </c>
       <c r="Q39">
-        <v>6.208989499999999</v>
+        <v>6.024773</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2832967085077019</v>
+        <v>0.2861570012673322</v>
       </c>
       <c r="T39">
-        <v>1.166909721651584</v>
+        <v>1.180963404538199</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.573501097159401</v>
+        <v>1.532093173549943</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1996473407857459</v>
+        <v>0.2172599358309537</v>
       </c>
       <c r="C40">
-        <v>233.4268890208392</v>
+        <v>194.0838294309855</v>
       </c>
       <c r="D40">
-        <v>352.3518890208392</v>
+        <v>316.1578294309855</v>
       </c>
       <c r="E40">
-        <v>95.96199999999999</v>
+        <v>99.11099999999999</v>
       </c>
       <c r="F40">
-        <v>119.662</v>
+        <v>122.811</v>
       </c>
       <c r="G40">
         <v>0.737</v>
@@ -4567,45 +4567,45 @@
         <v>16.5</v>
       </c>
       <c r="M40">
-        <v>10.76958</v>
+        <v>18.0286548</v>
       </c>
       <c r="N40">
-        <v>5.730420000000001</v>
+        <v>-1.528654800000002</v>
       </c>
       <c r="O40">
-        <v>2.005647</v>
+        <v>-0.5350291800000005</v>
       </c>
       <c r="P40">
-        <v>3.724773</v>
+        <v>-0.9936256200000012</v>
       </c>
       <c r="Q40">
-        <v>6.024773</v>
+        <v>1.306374379999998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2861570012673322</v>
+        <v>0.2923722805218795</v>
       </c>
       <c r="T40">
-        <v>1.180963404538199</v>
+        <v>1.211501384750567</v>
       </c>
       <c r="U40">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.35</v>
+        <v>0.3203233998356882</v>
       </c>
       <c r="W40">
-        <v>0.0585</v>
+        <v>0.09977652490412098</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>1.532093173549943</v>
+        <v>0.915209713816252</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2172599358309537</v>
+        <v>0.2182699358309537</v>
       </c>
       <c r="C41">
-        <v>194.0838294309855</v>
+        <v>189.0833797497015</v>
       </c>
       <c r="D41">
-        <v>316.1578294309855</v>
+        <v>314.3063797497015</v>
       </c>
       <c r="E41">
-        <v>99.11099999999999</v>
+        <v>102.26</v>
       </c>
       <c r="F41">
-        <v>122.811</v>
+        <v>125.96</v>
       </c>
       <c r="G41">
         <v>0.737</v>
@@ -4649,37 +4649,37 @@
         <v>16.5</v>
       </c>
       <c r="M41">
-        <v>18.0286548</v>
+        <v>18.490928</v>
       </c>
       <c r="N41">
-        <v>-1.528654800000002</v>
+        <v>-1.990928</v>
       </c>
       <c r="O41">
-        <v>-0.5350291800000005</v>
+        <v>-0.6968248</v>
       </c>
       <c r="P41">
-        <v>-0.9936256200000012</v>
+        <v>-1.2941032</v>
       </c>
       <c r="Q41">
-        <v>1.306374379999998</v>
+        <v>1.005896799999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2923722805218795</v>
+        <v>0.2964818185305775</v>
       </c>
       <c r="T41">
-        <v>1.211501384750567</v>
+        <v>1.23169307449641</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.3203233998356882</v>
+        <v>0.312315314839796</v>
       </c>
       <c r="W41">
-        <v>0.09977652490412098</v>
+        <v>0.100952111781518</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.915209713816252</v>
+        <v>0.8923294709708458</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2182699358309537</v>
+        <v>0.2192799358309537</v>
       </c>
       <c r="C42">
-        <v>189.0833797497015</v>
+        <v>184.1044883445274</v>
       </c>
       <c r="D42">
-        <v>314.3063797497015</v>
+        <v>312.4764883445274</v>
       </c>
       <c r="E42">
-        <v>102.26</v>
+        <v>105.409</v>
       </c>
       <c r="F42">
-        <v>125.96</v>
+        <v>129.109</v>
       </c>
       <c r="G42">
         <v>0.737</v>
@@ -4731,37 +4731,37 @@
         <v>16.5</v>
       </c>
       <c r="M42">
-        <v>18.490928</v>
+        <v>18.9532012</v>
       </c>
       <c r="N42">
-        <v>-1.990928</v>
+        <v>-2.453201200000002</v>
       </c>
       <c r="O42">
-        <v>-0.6968248</v>
+        <v>-0.8586204200000007</v>
       </c>
       <c r="P42">
-        <v>-1.2941032</v>
+        <v>-1.594580780000002</v>
       </c>
       <c r="Q42">
-        <v>1.005896799999999</v>
+        <v>0.7054192199999973</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2964818185305775</v>
+        <v>0.3007306629124518</v>
       </c>
       <c r="T42">
-        <v>1.23169307449641</v>
+        <v>1.252569228301434</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.312315314839796</v>
+        <v>0.3046978681363863</v>
       </c>
       <c r="W42">
-        <v>0.100952111781518</v>
+        <v>0.1020703529575785</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8923294709708458</v>
+        <v>0.8705653375325324</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2192799358309537</v>
+        <v>0.2202899358309537</v>
       </c>
       <c r="C43">
-        <v>184.1044883445274</v>
+        <v>179.1467808581901</v>
       </c>
       <c r="D43">
-        <v>312.4764883445274</v>
+        <v>310.6677808581901</v>
       </c>
       <c r="E43">
-        <v>105.409</v>
+        <v>108.558</v>
       </c>
       <c r="F43">
-        <v>129.109</v>
+        <v>132.258</v>
       </c>
       <c r="G43">
         <v>0.737</v>
@@ -4813,37 +4813,37 @@
         <v>16.5</v>
       </c>
       <c r="M43">
-        <v>18.9532012</v>
+        <v>19.4154744</v>
       </c>
       <c r="N43">
-        <v>-2.453201200000002</v>
+        <v>-2.915474400000004</v>
       </c>
       <c r="O43">
-        <v>-0.8586204200000007</v>
+        <v>-1.020416040000002</v>
       </c>
       <c r="P43">
-        <v>-1.594580780000002</v>
+        <v>-1.895058360000003</v>
       </c>
       <c r="Q43">
-        <v>0.7054192199999973</v>
+        <v>0.4049416399999961</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3007306629124518</v>
+        <v>0.305126019169563</v>
       </c>
       <c r="T43">
-        <v>1.252569228301434</v>
+        <v>1.274165249479045</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.3046978681363863</v>
+        <v>0.2974431569902818</v>
       </c>
       <c r="W43">
-        <v>0.1020703529575785</v>
+        <v>0.1031353445538266</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8705653375325324</v>
+        <v>0.8498375914008054</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2202899358309537</v>
+        <v>0.2212999358309537</v>
       </c>
       <c r="C44">
-        <v>179.1467808581901</v>
+        <v>174.2098915511022</v>
       </c>
       <c r="D44">
-        <v>310.66778085819</v>
+        <v>308.8798915511022</v>
       </c>
       <c r="E44">
-        <v>108.558</v>
+        <v>111.707</v>
       </c>
       <c r="F44">
-        <v>132.258</v>
+        <v>135.407</v>
       </c>
       <c r="G44">
         <v>0.737</v>
@@ -4895,37 +4895,37 @@
         <v>16.5</v>
       </c>
       <c r="M44">
-        <v>19.4154744</v>
+        <v>19.8777476</v>
       </c>
       <c r="N44">
-        <v>-2.915474400000001</v>
+        <v>-3.377747599999999</v>
       </c>
       <c r="O44">
-        <v>-1.02041604</v>
+        <v>-1.18221166</v>
       </c>
       <c r="P44">
-        <v>-1.895058360000001</v>
+        <v>-2.19553594</v>
       </c>
       <c r="Q44">
-        <v>0.4049416399999983</v>
+        <v>0.1044640599999993</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.305126019169563</v>
+        <v>0.3096755984532395</v>
       </c>
       <c r="T44">
-        <v>1.274165249479045</v>
+        <v>1.296519025785695</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2974431569902819</v>
+        <v>0.2905258742695777</v>
       </c>
       <c r="W44">
-        <v>0.1031353445538266</v>
+        <v>0.104150801657226</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8498375914008055</v>
+        <v>0.8300739264845077</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2212999358309537</v>
+        <v>0.2223099358309537</v>
       </c>
       <c r="C45">
-        <v>174.2098915511022</v>
+        <v>169.2934630548085</v>
       </c>
       <c r="D45">
-        <v>308.8798915511022</v>
+        <v>307.1124630548085</v>
       </c>
       <c r="E45">
-        <v>111.707</v>
+        <v>114.856</v>
       </c>
       <c r="F45">
-        <v>135.407</v>
+        <v>138.556</v>
       </c>
       <c r="G45">
         <v>0.737</v>
@@ -4977,37 +4977,37 @@
         <v>16.5</v>
       </c>
       <c r="M45">
-        <v>19.8777476</v>
+        <v>20.3400208</v>
       </c>
       <c r="N45">
-        <v>-3.377747599999999</v>
+        <v>-3.840020799999998</v>
       </c>
       <c r="O45">
-        <v>-1.18221166</v>
+        <v>-1.344007279999999</v>
       </c>
       <c r="P45">
-        <v>-2.19553594</v>
+        <v>-2.496013519999999</v>
       </c>
       <c r="Q45">
-        <v>0.1044640599999993</v>
+        <v>-0.1960135199999997</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3096755984532395</v>
+        <v>0.3143876627113331</v>
       </c>
       <c r="T45">
-        <v>1.296519025785695</v>
+        <v>1.319671151246154</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2905258742695777</v>
+        <v>0.2839230134907237</v>
       </c>
       <c r="W45">
-        <v>0.104150801657226</v>
+        <v>0.1051201016195618</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8300739264845077</v>
+        <v>0.8112086099734963</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2223099358309537</v>
+        <v>0.2533944133215194</v>
       </c>
       <c r="C46">
-        <v>169.2934630548085</v>
+        <v>120.1584931428245</v>
       </c>
       <c r="D46">
-        <v>307.1124630548085</v>
+        <v>261.1264931428244</v>
       </c>
       <c r="E46">
-        <v>114.856</v>
+        <v>118.005</v>
       </c>
       <c r="F46">
-        <v>138.556</v>
+        <v>141.705</v>
       </c>
       <c r="G46">
         <v>0.737</v>
@@ -5059,45 +5059,45 @@
         <v>16.5</v>
       </c>
       <c r="M46">
-        <v>20.3400208</v>
+        <v>28.454364</v>
       </c>
       <c r="N46">
-        <v>-3.840020799999998</v>
+        <v>-11.954364</v>
       </c>
       <c r="O46">
-        <v>-1.344007279999999</v>
+        <v>-4.184027399999999</v>
       </c>
       <c r="P46">
-        <v>-2.496013519999999</v>
+        <v>-7.770336599999999</v>
       </c>
       <c r="Q46">
-        <v>-0.1960135199999997</v>
+        <v>-5.4703366</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3143876627113331</v>
+        <v>0.3297701247434766</v>
       </c>
       <c r="T46">
-        <v>1.319671151246154</v>
+        <v>1.395250912334348</v>
       </c>
       <c r="U46">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.2839230134907237</v>
+        <v>0.202956565818867</v>
       </c>
       <c r="W46">
-        <v>0.1051201016195618</v>
+        <v>0.1600463215835715</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.8112086099734963</v>
+        <v>0.5798759023396201</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2533944133215194</v>
+        <v>0.2549444133215193</v>
       </c>
       <c r="C47">
-        <v>120.1584931428245</v>
+        <v>115.0742463057543</v>
       </c>
       <c r="D47">
-        <v>261.1264931428244</v>
+        <v>259.1912463057543</v>
       </c>
       <c r="E47">
-        <v>118.005</v>
+        <v>121.154</v>
       </c>
       <c r="F47">
-        <v>141.705</v>
+        <v>144.854</v>
       </c>
       <c r="G47">
         <v>0.737</v>
@@ -5141,37 +5141,37 @@
         <v>16.5</v>
       </c>
       <c r="M47">
-        <v>28.454364</v>
+        <v>29.0866832</v>
       </c>
       <c r="N47">
-        <v>-11.954364</v>
+        <v>-12.5866832</v>
       </c>
       <c r="O47">
-        <v>-4.184027399999999</v>
+        <v>-4.40533912</v>
       </c>
       <c r="P47">
-        <v>-7.770336599999999</v>
+        <v>-8.181344079999999</v>
       </c>
       <c r="Q47">
-        <v>-5.4703366</v>
+        <v>-5.88134408</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3297701247434766</v>
+        <v>0.3350288307572447</v>
       </c>
       <c r="T47">
-        <v>1.395250912334348</v>
+        <v>1.421088892192391</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.202956565818867</v>
+        <v>0.1985444665619351</v>
       </c>
       <c r="W47">
-        <v>0.1600463215835715</v>
+        <v>0.1609322711143634</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5798759023396201</v>
+        <v>0.5672699044626718</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2549444133215193</v>
+        <v>0.2564944133215193</v>
       </c>
       <c r="C48">
-        <v>115.0742463057543</v>
+        <v>110.0184732430967</v>
       </c>
       <c r="D48">
-        <v>259.1912463057543</v>
+        <v>257.2844732430967</v>
       </c>
       <c r="E48">
-        <v>121.154</v>
+        <v>124.303</v>
       </c>
       <c r="F48">
-        <v>144.854</v>
+        <v>148.003</v>
       </c>
       <c r="G48">
         <v>0.737</v>
@@ -5223,37 +5223,37 @@
         <v>16.5</v>
       </c>
       <c r="M48">
-        <v>29.0866832</v>
+        <v>29.7190024</v>
       </c>
       <c r="N48">
-        <v>-12.5866832</v>
+        <v>-13.2190024</v>
       </c>
       <c r="O48">
-        <v>-4.40533912</v>
+        <v>-4.626650839999999</v>
       </c>
       <c r="P48">
-        <v>-8.181344079999999</v>
+        <v>-8.592351559999997</v>
       </c>
       <c r="Q48">
-        <v>-5.88134408</v>
+        <v>-6.292351559999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3350288307572447</v>
+        <v>0.3404859785073814</v>
       </c>
       <c r="T48">
-        <v>1.421088892192391</v>
+        <v>1.447901890158286</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1985444665619351</v>
+        <v>0.1943201162095535</v>
       </c>
       <c r="W48">
-        <v>0.1609322711143634</v>
+        <v>0.1617805206651216</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5672699044626718</v>
+        <v>0.5552003320272958</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2564944133215193</v>
+        <v>0.2580444133215193</v>
       </c>
       <c r="C49">
-        <v>110.0184732430967</v>
+        <v>104.99055013136</v>
       </c>
       <c r="D49">
-        <v>257.2844732430967</v>
+        <v>255.40555013136</v>
       </c>
       <c r="E49">
-        <v>124.303</v>
+        <v>127.452</v>
       </c>
       <c r="F49">
-        <v>148.003</v>
+        <v>151.152</v>
       </c>
       <c r="G49">
         <v>0.737</v>
@@ -5305,37 +5305,37 @@
         <v>16.5</v>
       </c>
       <c r="M49">
-        <v>29.7190024</v>
+        <v>30.3513216</v>
       </c>
       <c r="N49">
-        <v>-13.2190024</v>
+        <v>-13.8513216</v>
       </c>
       <c r="O49">
-        <v>-4.626650839999999</v>
+        <v>-4.847962559999999</v>
       </c>
       <c r="P49">
-        <v>-8.592351559999997</v>
+        <v>-9.003359039999999</v>
       </c>
       <c r="Q49">
-        <v>-6.292351559999998</v>
+        <v>-6.70335904</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3404859785073814</v>
+        <v>0.3461530165556003</v>
       </c>
       <c r="T49">
-        <v>1.447901890158286</v>
+        <v>1.475746157276714</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1943201162095535</v>
+        <v>0.1902717804551878</v>
       </c>
       <c r="W49">
-        <v>0.1617805206651216</v>
+        <v>0.1625934264845983</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5552003320272958</v>
+        <v>0.5436336584433938</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2580444133215193</v>
+        <v>0.2595944133215193</v>
       </c>
       <c r="C50">
-        <v>104.99055013136</v>
+        <v>99.98987123782285</v>
       </c>
       <c r="D50">
-        <v>255.40555013136</v>
+        <v>253.5538712378228</v>
       </c>
       <c r="E50">
-        <v>127.452</v>
+        <v>130.601</v>
       </c>
       <c r="F50">
-        <v>151.152</v>
+        <v>154.301</v>
       </c>
       <c r="G50">
         <v>0.737</v>
@@ -5387,37 +5387,37 @@
         <v>16.5</v>
       </c>
       <c r="M50">
-        <v>30.3513216</v>
+        <v>30.9836408</v>
       </c>
       <c r="N50">
-        <v>-13.8513216</v>
+        <v>-14.4836408</v>
       </c>
       <c r="O50">
-        <v>-4.847962559999999</v>
+        <v>-5.069274279999999</v>
       </c>
       <c r="P50">
-        <v>-9.003359039999999</v>
+        <v>-9.414366520000002</v>
       </c>
       <c r="Q50">
-        <v>-6.70335904</v>
+        <v>-7.114366520000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3461530165556002</v>
+        <v>0.3520422913900238</v>
       </c>
       <c r="T50">
-        <v>1.475746157276714</v>
+        <v>1.504682356439003</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1902717804551878</v>
+        <v>0.1863886828948779</v>
       </c>
       <c r="W50">
-        <v>0.1625934264845983</v>
+        <v>0.1633731524747085</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5436336584433938</v>
+        <v>0.5325390939853654</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2595944133215193</v>
+        <v>0.2611444133215193</v>
       </c>
       <c r="C51">
-        <v>99.98987123782285</v>
+        <v>95.01584826946817</v>
       </c>
       <c r="D51">
-        <v>253.5538712378228</v>
+        <v>251.7288482694682</v>
       </c>
       <c r="E51">
-        <v>130.601</v>
+        <v>133.75</v>
       </c>
       <c r="F51">
-        <v>154.301</v>
+        <v>157.45</v>
       </c>
       <c r="G51">
         <v>0.737</v>
@@ -5469,37 +5469,37 @@
         <v>16.5</v>
       </c>
       <c r="M51">
-        <v>30.9836408</v>
+        <v>31.61596</v>
       </c>
       <c r="N51">
-        <v>-14.4836408</v>
+        <v>-15.11596</v>
       </c>
       <c r="O51">
-        <v>-5.069274279999999</v>
+        <v>-5.290585999999998</v>
       </c>
       <c r="P51">
-        <v>-9.414366520000002</v>
+        <v>-9.825374</v>
       </c>
       <c r="Q51">
-        <v>-7.114366520000003</v>
+        <v>-7.525374000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3520422913900238</v>
+        <v>0.3581671372178243</v>
       </c>
       <c r="T51">
-        <v>1.504682356439003</v>
+        <v>1.534776003567783</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1863886828948779</v>
+        <v>0.1826609092369803</v>
       </c>
       <c r="W51">
-        <v>0.1633731524747085</v>
+        <v>0.1641216894252144</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5325390939853654</v>
+        <v>0.5218883121056581</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2611444133215193</v>
+        <v>0.2626944133215193</v>
       </c>
       <c r="C52">
-        <v>95.01584826946817</v>
+        <v>90.06790974983335</v>
       </c>
       <c r="D52">
-        <v>251.7288482694682</v>
+        <v>249.9299097498333</v>
       </c>
       <c r="E52">
-        <v>133.75</v>
+        <v>136.899</v>
       </c>
       <c r="F52">
-        <v>157.45</v>
+        <v>160.599</v>
       </c>
       <c r="G52">
         <v>0.737</v>
@@ -5551,37 +5551,37 @@
         <v>16.5</v>
       </c>
       <c r="M52">
-        <v>31.61596</v>
+        <v>32.2482792</v>
       </c>
       <c r="N52">
-        <v>-15.11596</v>
+        <v>-15.7482792</v>
       </c>
       <c r="O52">
-        <v>-5.290585999999998</v>
+        <v>-5.511897719999999</v>
       </c>
       <c r="P52">
-        <v>-9.825374</v>
+        <v>-10.23638148</v>
       </c>
       <c r="Q52">
-        <v>-7.525374000000001</v>
+        <v>-7.93638148</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3581671372178243</v>
+        <v>0.3645419767528819</v>
       </c>
       <c r="T52">
-        <v>1.534776003567783</v>
+        <v>1.566097962824268</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1826609092369803</v>
+        <v>0.1790793227813532</v>
       </c>
       <c r="W52">
-        <v>0.1641216894252144</v>
+        <v>0.1648408719855043</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5218883121056581</v>
+        <v>0.5116552079467236</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2626944133215193</v>
+        <v>0.2642444133215193</v>
       </c>
       <c r="C53">
-        <v>90.06790974983335</v>
+        <v>85.14550042239017</v>
       </c>
       <c r="D53">
-        <v>249.9299097498333</v>
+        <v>248.1565004223902</v>
       </c>
       <c r="E53">
-        <v>136.899</v>
+        <v>140.048</v>
       </c>
       <c r="F53">
-        <v>160.599</v>
+        <v>163.748</v>
       </c>
       <c r="G53">
         <v>0.737</v>
@@ -5633,37 +5633,37 @@
         <v>16.5</v>
       </c>
       <c r="M53">
-        <v>32.2482792</v>
+        <v>32.8805984</v>
       </c>
       <c r="N53">
-        <v>-15.7482792</v>
+        <v>-16.3805984</v>
       </c>
       <c r="O53">
-        <v>-5.511897719999999</v>
+        <v>-5.733209439999999</v>
       </c>
       <c r="P53">
-        <v>-10.23638148</v>
+        <v>-10.64738896</v>
       </c>
       <c r="Q53">
-        <v>-7.93638148</v>
+        <v>-8.347388959999998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3645419767528819</v>
+        <v>0.3711824346019003</v>
       </c>
       <c r="T53">
-        <v>1.566097962824268</v>
+        <v>1.598725003716441</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1790793227813532</v>
+        <v>0.1756354896509426</v>
       </c>
       <c r="W53">
-        <v>0.1648408719855043</v>
+        <v>0.1655323936780907</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5116552079467236</v>
+        <v>0.5018156847169789</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2642444133215193</v>
+        <v>0.2866744847369158</v>
       </c>
       <c r="C54">
-        <v>85.14550042239017</v>
+        <v>58.88833256165356</v>
       </c>
       <c r="D54">
-        <v>248.1565004223902</v>
+        <v>225.0483325616536</v>
       </c>
       <c r="E54">
-        <v>140.048</v>
+        <v>143.197</v>
       </c>
       <c r="F54">
-        <v>163.748</v>
+        <v>166.897</v>
       </c>
       <c r="G54">
         <v>0.737</v>
@@ -5715,45 +5715,45 @@
         <v>16.5</v>
       </c>
       <c r="M54">
-        <v>32.8805984</v>
+        <v>39.3543126</v>
       </c>
       <c r="N54">
-        <v>-16.3805984</v>
+        <v>-22.8543126</v>
       </c>
       <c r="O54">
-        <v>-5.733209439999999</v>
+        <v>-7.999009409999999</v>
       </c>
       <c r="P54">
-        <v>-10.64738896</v>
+        <v>-14.85530319</v>
       </c>
       <c r="Q54">
-        <v>-8.347388959999998</v>
+        <v>-12.55530319</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3711824346019003</v>
+        <v>0.3830630638815077</v>
       </c>
       <c r="T54">
-        <v>1.598725003716441</v>
+        <v>1.6570989571612</v>
       </c>
       <c r="U54">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1756354896509426</v>
+        <v>0.146743765002263</v>
       </c>
       <c r="W54">
-        <v>0.1655323936780907</v>
+        <v>0.2011978202124664</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.5018156847169789</v>
+        <v>0.4192679000064659</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2866744847369158</v>
+        <v>0.2885744847369158</v>
       </c>
       <c r="C55">
-        <v>58.88833256165356</v>
+        <v>53.97806085169404</v>
       </c>
       <c r="D55">
-        <v>225.0483325616536</v>
+        <v>223.287060851694</v>
       </c>
       <c r="E55">
-        <v>143.197</v>
+        <v>146.346</v>
       </c>
       <c r="F55">
-        <v>166.897</v>
+        <v>170.046</v>
       </c>
       <c r="G55">
         <v>0.737</v>
@@ -5797,37 +5797,37 @@
         <v>16.5</v>
       </c>
       <c r="M55">
-        <v>39.3543126</v>
+        <v>40.0968468</v>
       </c>
       <c r="N55">
-        <v>-22.8543126</v>
+        <v>-23.5968468</v>
       </c>
       <c r="O55">
-        <v>-7.999009409999999</v>
+        <v>-8.258896379999999</v>
       </c>
       <c r="P55">
-        <v>-14.85530319</v>
+        <v>-15.33795042</v>
       </c>
       <c r="Q55">
-        <v>-12.55530319</v>
+        <v>-13.03795042</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3830630638815077</v>
+        <v>0.3903948696180622</v>
       </c>
       <c r="T55">
-        <v>1.6570989571612</v>
+        <v>1.69312284753427</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.146743765002263</v>
+        <v>0.1440262878725915</v>
       </c>
       <c r="W55">
-        <v>0.2011978202124664</v>
+        <v>0.2018386013196429</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4192679000064659</v>
+        <v>0.4115036796359758</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2885744847369158</v>
+        <v>0.2904744847369158</v>
       </c>
       <c r="C56">
-        <v>53.97806085169404</v>
+        <v>49.09514316888217</v>
       </c>
       <c r="D56">
-        <v>223.287060851694</v>
+        <v>221.5531431688822</v>
       </c>
       <c r="E56">
-        <v>146.346</v>
+        <v>149.495</v>
       </c>
       <c r="F56">
-        <v>170.046</v>
+        <v>173.195</v>
       </c>
       <c r="G56">
         <v>0.737</v>
@@ -5879,37 +5879,37 @@
         <v>16.5</v>
       </c>
       <c r="M56">
-        <v>40.0968468</v>
+        <v>40.839381</v>
       </c>
       <c r="N56">
-        <v>-23.5968468</v>
+        <v>-24.339381</v>
       </c>
       <c r="O56">
-        <v>-8.258896379999999</v>
+        <v>-8.51878335</v>
       </c>
       <c r="P56">
-        <v>-15.33795042</v>
+        <v>-15.82059765</v>
       </c>
       <c r="Q56">
-        <v>-13.03795042</v>
+        <v>-13.52059765</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3903948696180622</v>
+        <v>0.3980525333873525</v>
       </c>
       <c r="T56">
-        <v>1.69312284753427</v>
+        <v>1.730747799701698</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1440262878725915</v>
+        <v>0.1414076280930898</v>
       </c>
       <c r="W56">
-        <v>0.2018386013196429</v>
+        <v>0.2024560812956494</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4115036796359758</v>
+        <v>0.4040217945516853</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2904744847369158</v>
+        <v>0.2923744847369157</v>
       </c>
       <c r="C57">
-        <v>49.09514316888217</v>
+        <v>44.23894717709086</v>
       </c>
       <c r="D57">
-        <v>221.5531431688822</v>
+        <v>219.8459471770909</v>
       </c>
       <c r="E57">
-        <v>149.495</v>
+        <v>152.644</v>
       </c>
       <c r="F57">
-        <v>173.195</v>
+        <v>176.344</v>
       </c>
       <c r="G57">
         <v>0.737</v>
@@ -5961,37 +5961,37 @@
         <v>16.5</v>
       </c>
       <c r="M57">
-        <v>40.839381</v>
+        <v>41.5819152</v>
       </c>
       <c r="N57">
-        <v>-24.339381</v>
+        <v>-25.0819152</v>
       </c>
       <c r="O57">
-        <v>-8.51878335</v>
+        <v>-8.778670319999998</v>
       </c>
       <c r="P57">
-        <v>-15.82059765</v>
+        <v>-16.30324488</v>
       </c>
       <c r="Q57">
-        <v>-13.52059765</v>
+        <v>-14.00324488</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3980525333873525</v>
+        <v>0.4060582727825195</v>
       </c>
       <c r="T57">
-        <v>1.730747799701698</v>
+        <v>1.770082976967646</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1414076280930898</v>
+        <v>0.1388824918771418</v>
       </c>
       <c r="W57">
-        <v>0.2024560812956494</v>
+        <v>0.20305150841537</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4040217945516853</v>
+        <v>0.3968071196489766</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2923744847369157</v>
+        <v>0.2942744847369158</v>
       </c>
       <c r="C58">
-        <v>44.23894717709086</v>
+        <v>39.40885988123134</v>
       </c>
       <c r="D58">
-        <v>219.8459471770909</v>
+        <v>218.1648598812313</v>
       </c>
       <c r="E58">
-        <v>152.644</v>
+        <v>155.793</v>
       </c>
       <c r="F58">
-        <v>176.344</v>
+        <v>179.493</v>
       </c>
       <c r="G58">
         <v>0.737</v>
@@ -6043,37 +6043,37 @@
         <v>16.5</v>
       </c>
       <c r="M58">
-        <v>41.5819152</v>
+        <v>42.3244494</v>
       </c>
       <c r="N58">
-        <v>-25.0819152</v>
+        <v>-25.8244494</v>
       </c>
       <c r="O58">
-        <v>-8.778670319999998</v>
+        <v>-9.038557289999998</v>
       </c>
       <c r="P58">
-        <v>-16.30324488</v>
+        <v>-16.78589211</v>
       </c>
       <c r="Q58">
-        <v>-14.00324488</v>
+        <v>-14.48589211</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4060582727825195</v>
+        <v>0.4144363721495549</v>
       </c>
       <c r="T58">
-        <v>1.770082976967646</v>
+        <v>1.811247697362242</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1388824918771418</v>
+        <v>0.1364459569319288</v>
       </c>
       <c r="W58">
-        <v>0.20305150841537</v>
+        <v>0.2036260433554512</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3968071196489766</v>
+        <v>0.3898455912340824</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2942744847369158</v>
+        <v>0.2961744847369158</v>
       </c>
       <c r="C59">
-        <v>39.40885988123134</v>
+        <v>34.60428689339312</v>
       </c>
       <c r="D59">
-        <v>218.1648598812313</v>
+        <v>216.5092868933931</v>
       </c>
       <c r="E59">
-        <v>155.793</v>
+        <v>158.942</v>
       </c>
       <c r="F59">
-        <v>179.493</v>
+        <v>182.642</v>
       </c>
       <c r="G59">
         <v>0.737</v>
@@ -6125,37 +6125,37 @@
         <v>16.5</v>
       </c>
       <c r="M59">
-        <v>42.3244494</v>
+        <v>43.0669836</v>
       </c>
       <c r="N59">
-        <v>-25.8244494</v>
+        <v>-26.5669836</v>
       </c>
       <c r="O59">
-        <v>-9.038557289999998</v>
+        <v>-9.29844426</v>
       </c>
       <c r="P59">
-        <v>-16.78589211</v>
+        <v>-17.26853934</v>
       </c>
       <c r="Q59">
-        <v>-14.48589211</v>
+        <v>-14.96853934</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4144363721495549</v>
+        <v>0.4232134286293062</v>
       </c>
       <c r="T59">
-        <v>1.811247697362242</v>
+        <v>1.854372642537534</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1364459569319288</v>
+        <v>0.1340934404331024</v>
       </c>
       <c r="W59">
-        <v>0.2036260433554512</v>
+        <v>0.2041807667458745</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3898455912340824</v>
+        <v>0.3831241155231498</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2961744847369158</v>
+        <v>0.2980744847369158</v>
       </c>
       <c r="C60">
-        <v>34.60428689339315</v>
+        <v>29.82465173214632</v>
       </c>
       <c r="D60">
-        <v>216.5092868933931</v>
+        <v>214.8786517321463</v>
       </c>
       <c r="E60">
-        <v>158.942</v>
+        <v>162.091</v>
       </c>
       <c r="F60">
-        <v>182.642</v>
+        <v>185.791</v>
       </c>
       <c r="G60">
         <v>0.737</v>
@@ -6207,37 +6207,37 @@
         <v>16.5</v>
       </c>
       <c r="M60">
-        <v>43.06698359999999</v>
+        <v>43.80951779999999</v>
       </c>
       <c r="N60">
-        <v>-26.56698359999999</v>
+        <v>-27.30951779999999</v>
       </c>
       <c r="O60">
-        <v>-9.298444259999997</v>
+        <v>-9.558331229999997</v>
       </c>
       <c r="P60">
-        <v>-17.26853934</v>
+        <v>-17.75118657</v>
       </c>
       <c r="Q60">
-        <v>-14.96853934</v>
+        <v>-15.45118657</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4232134286293061</v>
+        <v>0.4324186342056306</v>
       </c>
       <c r="T60">
-        <v>1.854372642537533</v>
+        <v>1.899601243575034</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1340934404331025</v>
+        <v>0.1318206702562702</v>
       </c>
       <c r="W60">
-        <v>0.2041807667458745</v>
+        <v>0.2047166859535715</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.38312411552315</v>
+        <v>0.3766304864464863</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2980744847369158</v>
+        <v>0.2999744847369157</v>
       </c>
       <c r="C61">
-        <v>29.82465173214632</v>
+        <v>25.06939515327039</v>
       </c>
       <c r="D61">
-        <v>214.8786517321463</v>
+        <v>213.2723951532704</v>
       </c>
       <c r="E61">
-        <v>162.091</v>
+        <v>165.24</v>
       </c>
       <c r="F61">
-        <v>185.791</v>
+        <v>188.94</v>
       </c>
       <c r="G61">
         <v>0.737</v>
@@ -6289,37 +6289,37 @@
         <v>16.5</v>
       </c>
       <c r="M61">
-        <v>43.80951779999999</v>
+        <v>44.552052</v>
       </c>
       <c r="N61">
-        <v>-27.30951779999999</v>
+        <v>-28.052052</v>
       </c>
       <c r="O61">
-        <v>-9.558331229999997</v>
+        <v>-9.818218199999999</v>
       </c>
       <c r="P61">
-        <v>-17.75118657</v>
+        <v>-18.2338338</v>
       </c>
       <c r="Q61">
-        <v>-15.45118657</v>
+        <v>-15.9338338</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4324186342056306</v>
+        <v>0.4420841000607714</v>
       </c>
       <c r="T61">
-        <v>1.899601243575034</v>
+        <v>1.94709127466441</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1318206702562702</v>
+        <v>0.1296236590853324</v>
       </c>
       <c r="W61">
-        <v>0.2047166859535715</v>
+        <v>0.2052347411876786</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3766304864464863</v>
+        <v>0.3703533116723782</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2999744847369157</v>
+        <v>0.3018744847369158</v>
       </c>
       <c r="C62">
-        <v>25.06939515327039</v>
+        <v>20.33797451027843</v>
       </c>
       <c r="D62">
-        <v>213.2723951532704</v>
+        <v>211.6899745102784</v>
       </c>
       <c r="E62">
-        <v>165.24</v>
+        <v>168.389</v>
       </c>
       <c r="F62">
-        <v>188.94</v>
+        <v>192.089</v>
       </c>
       <c r="G62">
         <v>0.737</v>
@@ -6371,37 +6371,37 @@
         <v>16.5</v>
       </c>
       <c r="M62">
-        <v>44.552052</v>
+        <v>45.2945862</v>
       </c>
       <c r="N62">
-        <v>-28.052052</v>
+        <v>-28.7945862</v>
       </c>
       <c r="O62">
-        <v>-9.818218199999999</v>
+        <v>-10.07810517</v>
       </c>
       <c r="P62">
-        <v>-18.2338338</v>
+        <v>-18.71648103</v>
       </c>
       <c r="Q62">
-        <v>-15.9338338</v>
+        <v>-16.41648103</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4420841000607714</v>
+        <v>0.4522452308315605</v>
       </c>
       <c r="T62">
-        <v>1.94709127466441</v>
+        <v>1.997016691963498</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1296236590853324</v>
+        <v>0.12749868106754</v>
       </c>
       <c r="W62">
-        <v>0.2052347411876786</v>
+        <v>0.2057358110042741</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3703533116723782</v>
+        <v>0.3642819459072573</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3018744847369158</v>
+        <v>0.3037744847369158</v>
       </c>
       <c r="C63">
-        <v>20.33797451027843</v>
+        <v>15.6298631432</v>
       </c>
       <c r="D63">
-        <v>211.6899745102784</v>
+        <v>210.1308631432</v>
       </c>
       <c r="E63">
-        <v>168.389</v>
+        <v>171.538</v>
       </c>
       <c r="F63">
-        <v>192.089</v>
+        <v>195.238</v>
       </c>
       <c r="G63">
         <v>0.737</v>
@@ -6453,37 +6453,37 @@
         <v>16.5</v>
       </c>
       <c r="M63">
-        <v>45.2945862</v>
+        <v>46.03712039999999</v>
       </c>
       <c r="N63">
-        <v>-28.7945862</v>
+        <v>-29.53712039999999</v>
       </c>
       <c r="O63">
-        <v>-10.07810517</v>
+        <v>-10.33799214</v>
       </c>
       <c r="P63">
-        <v>-18.71648103</v>
+        <v>-19.19912825999999</v>
       </c>
       <c r="Q63">
-        <v>-16.41648103</v>
+        <v>-16.89912826</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4522452308315605</v>
+        <v>0.4629411579587068</v>
       </c>
       <c r="T63">
-        <v>1.997016691963498</v>
+        <v>2.049569762804643</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.12749868106754</v>
+        <v>0.125442250727741</v>
       </c>
       <c r="W63">
-        <v>0.2057358110042741</v>
+        <v>0.2062207172783987</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3642819459072573</v>
+        <v>0.3584064306506887</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3037744847369158</v>
+        <v>0.3056744847369158</v>
       </c>
       <c r="C64">
-        <v>15.6298631432</v>
+        <v>10.94454979417588</v>
       </c>
       <c r="D64">
-        <v>210.1308631432</v>
+        <v>208.5945497941759</v>
       </c>
       <c r="E64">
-        <v>171.538</v>
+        <v>174.687</v>
       </c>
       <c r="F64">
-        <v>195.238</v>
+        <v>198.387</v>
       </c>
       <c r="G64">
         <v>0.737</v>
@@ -6535,37 +6535,37 @@
         <v>16.5</v>
       </c>
       <c r="M64">
-        <v>46.03712039999999</v>
+        <v>46.7796546</v>
       </c>
       <c r="N64">
-        <v>-29.53712039999999</v>
+        <v>-30.2796546</v>
       </c>
       <c r="O64">
-        <v>-10.33799214</v>
+        <v>-10.59787911</v>
       </c>
       <c r="P64">
-        <v>-19.19912825999999</v>
+        <v>-19.68177549</v>
       </c>
       <c r="Q64">
-        <v>-16.89912826</v>
+        <v>-17.38177549</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4629411579587068</v>
+        <v>0.4742152433089421</v>
       </c>
       <c r="T64">
-        <v>2.049569762804643</v>
+        <v>2.104963540177741</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.125442250727741</v>
+        <v>0.1234511038907927</v>
       </c>
       <c r="W64">
-        <v>0.2062207172783987</v>
+        <v>0.2066902297025511</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3584064306506887</v>
+        <v>0.3527174396879792</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3056744847369158</v>
+        <v>0.3075744847369158</v>
       </c>
       <c r="C65">
-        <v>10.94454979417588</v>
+        <v>6.281538048503847</v>
       </c>
       <c r="D65">
-        <v>208.5945497941759</v>
+        <v>207.0805380485039</v>
       </c>
       <c r="E65">
-        <v>174.687</v>
+        <v>177.836</v>
       </c>
       <c r="F65">
-        <v>198.387</v>
+        <v>201.536</v>
       </c>
       <c r="G65">
         <v>0.737</v>
@@ -6617,37 +6617,37 @@
         <v>16.5</v>
       </c>
       <c r="M65">
-        <v>46.7796546</v>
+        <v>47.5221888</v>
       </c>
       <c r="N65">
-        <v>-30.2796546</v>
+        <v>-31.0221888</v>
       </c>
       <c r="O65">
-        <v>-10.59787911</v>
+        <v>-10.85776608</v>
       </c>
       <c r="P65">
-        <v>-19.68177549</v>
+        <v>-20.16442272</v>
       </c>
       <c r="Q65">
-        <v>-17.38177549</v>
+        <v>-17.86442272000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4742152433089421</v>
+        <v>0.4861156667341906</v>
       </c>
       <c r="T65">
-        <v>2.104963540177741</v>
+        <v>2.163434749627123</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1234511038907927</v>
+        <v>0.1215221803924991</v>
       </c>
       <c r="W65">
-        <v>0.2066902297025511</v>
+        <v>0.2071450698634487</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3527174396879792</v>
+        <v>0.3472062296928545</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3075744847369158</v>
+        <v>0.3094744847369158</v>
       </c>
       <c r="C66">
-        <v>6.281538048503847</v>
+        <v>1.640345799850223</v>
       </c>
       <c r="D66">
-        <v>207.0805380485039</v>
+        <v>205.5883457998502</v>
       </c>
       <c r="E66">
-        <v>177.836</v>
+        <v>180.985</v>
       </c>
       <c r="F66">
-        <v>201.536</v>
+        <v>204.685</v>
       </c>
       <c r="G66">
         <v>0.737</v>
@@ -6699,37 +6699,37 @@
         <v>16.5</v>
       </c>
       <c r="M66">
-        <v>47.5221888</v>
+        <v>48.264723</v>
       </c>
       <c r="N66">
-        <v>-31.0221888</v>
+        <v>-31.764723</v>
       </c>
       <c r="O66">
-        <v>-10.85776608</v>
+        <v>-11.11765305</v>
       </c>
       <c r="P66">
-        <v>-20.16442272</v>
+        <v>-20.64706995</v>
       </c>
       <c r="Q66">
-        <v>-17.86442272000001</v>
+        <v>-18.34706995000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4861156667341906</v>
+        <v>0.4986961143551675</v>
       </c>
       <c r="T66">
-        <v>2.163434749627123</v>
+        <v>2.225247171045041</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1215221803924991</v>
+        <v>0.1196526083864606</v>
       </c>
       <c r="W66">
-        <v>0.2071450698634487</v>
+        <v>0.2075859149424726</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3472062296928545</v>
+        <v>0.3418645953898876</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3094744847369158</v>
+        <v>0.3113744847369158</v>
       </c>
       <c r="C67">
-        <v>1.640345799850223</v>
+        <v>-2.979495261581746</v>
       </c>
       <c r="D67">
-        <v>205.5883457998502</v>
+        <v>204.1175047384183</v>
       </c>
       <c r="E67">
-        <v>180.985</v>
+        <v>184.134</v>
       </c>
       <c r="F67">
-        <v>204.685</v>
+        <v>207.834</v>
       </c>
       <c r="G67">
         <v>0.737</v>
@@ -6781,37 +6781,37 @@
         <v>16.5</v>
       </c>
       <c r="M67">
-        <v>48.264723</v>
+        <v>49.00725720000001</v>
       </c>
       <c r="N67">
-        <v>-31.764723</v>
+        <v>-32.50725720000001</v>
       </c>
       <c r="O67">
-        <v>-11.11765305</v>
+        <v>-11.37754002</v>
       </c>
       <c r="P67">
-        <v>-20.64706995</v>
+        <v>-21.12971718</v>
       </c>
       <c r="Q67">
-        <v>-18.34706995000001</v>
+        <v>-18.82971718</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4986961143551675</v>
+        <v>0.51201658830679</v>
       </c>
       <c r="T67">
-        <v>2.225247171045041</v>
+        <v>2.290695617252247</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1196526083864606</v>
+        <v>0.1178396900775749</v>
       </c>
       <c r="W67">
-        <v>0.2075859149424726</v>
+        <v>0.2080134010797078</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3418645953898876</v>
+        <v>0.336684828793071</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3113744847369158</v>
+        <v>0.3132744847369158</v>
       </c>
       <c r="C68">
-        <v>-2.979495261581746</v>
+        <v>-7.57844013906967</v>
       </c>
       <c r="D68">
-        <v>204.1175047384183</v>
+        <v>202.6675598609303</v>
       </c>
       <c r="E68">
-        <v>184.134</v>
+        <v>187.283</v>
       </c>
       <c r="F68">
-        <v>207.834</v>
+        <v>210.983</v>
       </c>
       <c r="G68">
         <v>0.737</v>
@@ -6863,37 +6863,37 @@
         <v>16.5</v>
       </c>
       <c r="M68">
-        <v>49.00725720000001</v>
+        <v>49.7497914</v>
       </c>
       <c r="N68">
-        <v>-32.50725720000001</v>
+        <v>-33.2497914</v>
       </c>
       <c r="O68">
-        <v>-11.37754002</v>
+        <v>-11.63742699</v>
       </c>
       <c r="P68">
-        <v>-21.12971718</v>
+        <v>-21.61236441</v>
       </c>
       <c r="Q68">
-        <v>-18.82971718</v>
+        <v>-19.31236441</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.51201658830679</v>
+        <v>0.5261443637100262</v>
       </c>
       <c r="T68">
-        <v>2.290695617252247</v>
+        <v>2.360110635956862</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1178396900775749</v>
+        <v>0.1160808887331335</v>
       </c>
       <c r="W68">
-        <v>0.2080134010797078</v>
+        <v>0.2084281264367271</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.336684828793071</v>
+        <v>0.331659682094667</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3132744847369158</v>
+        <v>0.3151744847369158</v>
       </c>
       <c r="C69">
-        <v>-7.57844013906967</v>
+        <v>-12.15693099865067</v>
       </c>
       <c r="D69">
-        <v>202.6675598609303</v>
+        <v>201.2380690013493</v>
       </c>
       <c r="E69">
-        <v>187.283</v>
+        <v>190.432</v>
       </c>
       <c r="F69">
-        <v>210.983</v>
+        <v>214.132</v>
       </c>
       <c r="G69">
         <v>0.737</v>
@@ -6945,37 +6945,37 @@
         <v>16.5</v>
       </c>
       <c r="M69">
-        <v>49.7497914</v>
+        <v>50.4923256</v>
       </c>
       <c r="N69">
-        <v>-33.2497914</v>
+        <v>-33.9923256</v>
       </c>
       <c r="O69">
-        <v>-11.63742699</v>
+        <v>-11.89731396</v>
       </c>
       <c r="P69">
-        <v>-21.61236441</v>
+        <v>-22.09501164</v>
       </c>
       <c r="Q69">
-        <v>-19.31236441</v>
+        <v>-19.79501164000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5261443637100262</v>
+        <v>0.5411551250759644</v>
       </c>
       <c r="T69">
-        <v>2.360110635956862</v>
+        <v>2.433864093330513</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1160808887331335</v>
+        <v>0.1143738168399991</v>
       </c>
       <c r="W69">
-        <v>0.2084281264367271</v>
+        <v>0.2088306539891282</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.331659682094667</v>
+        <v>0.326782333828569</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3151744847369158</v>
+        <v>0.3170744847369158</v>
       </c>
       <c r="C70">
-        <v>-12.15693099865067</v>
+        <v>-16.71539761868084</v>
       </c>
       <c r="D70">
-        <v>201.2380690013493</v>
+        <v>199.8286023813192</v>
       </c>
       <c r="E70">
-        <v>190.432</v>
+        <v>193.581</v>
       </c>
       <c r="F70">
-        <v>214.132</v>
+        <v>217.281</v>
       </c>
       <c r="G70">
         <v>0.737</v>
@@ -7027,37 +7027,37 @@
         <v>16.5</v>
       </c>
       <c r="M70">
-        <v>50.4923256</v>
+        <v>51.2348598</v>
       </c>
       <c r="N70">
-        <v>-33.9923256</v>
+        <v>-34.7348598</v>
       </c>
       <c r="O70">
-        <v>-11.89731396</v>
+        <v>-12.15720093</v>
       </c>
       <c r="P70">
-        <v>-22.09501164</v>
+        <v>-22.57765887</v>
       </c>
       <c r="Q70">
-        <v>-19.79501164000001</v>
+        <v>-20.27765887</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5411551250759644</v>
+        <v>0.5571343226590602</v>
       </c>
       <c r="T70">
-        <v>2.433864093330513</v>
+        <v>2.51237583827666</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1143738168399991</v>
+        <v>0.1127162252915933</v>
       </c>
       <c r="W70">
-        <v>0.2088306539891282</v>
+        <v>0.2092215140762423</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.326782333828569</v>
+        <v>0.322046357975981</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3170744847369158</v>
+        <v>0.3189744847369158</v>
       </c>
       <c r="C71">
-        <v>-16.71539761868084</v>
+        <v>-21.25425782063255</v>
       </c>
       <c r="D71">
-        <v>199.8286023813192</v>
+        <v>198.4387421793675</v>
       </c>
       <c r="E71">
-        <v>193.581</v>
+        <v>196.73</v>
       </c>
       <c r="F71">
-        <v>217.281</v>
+        <v>220.43</v>
       </c>
       <c r="G71">
         <v>0.737</v>
@@ -7109,37 +7109,37 @@
         <v>16.5</v>
       </c>
       <c r="M71">
-        <v>51.2348598</v>
+        <v>51.977394</v>
       </c>
       <c r="N71">
-        <v>-34.7348598</v>
+        <v>-35.477394</v>
       </c>
       <c r="O71">
-        <v>-12.15720093</v>
+        <v>-12.4170879</v>
       </c>
       <c r="P71">
-        <v>-22.57765887</v>
+        <v>-23.06030610000001</v>
       </c>
       <c r="Q71">
-        <v>-20.27765887</v>
+        <v>-20.76030610000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5571343226590602</v>
+        <v>0.5741788000810286</v>
       </c>
       <c r="T71">
-        <v>2.51237583827666</v>
+        <v>2.596121699552548</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1127162252915933</v>
+        <v>0.1111059935017134</v>
       </c>
       <c r="W71">
-        <v>0.2092215140762423</v>
+        <v>0.209601206732296</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.322046357975981</v>
+        <v>0.3174456957191812</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3189744847369158</v>
+        <v>0.3208744847369158</v>
       </c>
       <c r="C72">
-        <v>-21.25425782063255</v>
+        <v>-25.77391788203886</v>
       </c>
       <c r="D72">
-        <v>198.4387421793675</v>
+        <v>197.0680821179612</v>
       </c>
       <c r="E72">
-        <v>196.73</v>
+        <v>199.879</v>
       </c>
       <c r="F72">
-        <v>220.43</v>
+        <v>223.579</v>
       </c>
       <c r="G72">
         <v>0.737</v>
@@ -7191,37 +7191,37 @@
         <v>16.5</v>
       </c>
       <c r="M72">
-        <v>51.977394</v>
+        <v>52.71992820000001</v>
       </c>
       <c r="N72">
-        <v>-35.477394</v>
+        <v>-36.21992820000001</v>
       </c>
       <c r="O72">
-        <v>-12.4170879</v>
+        <v>-12.67697487</v>
       </c>
       <c r="P72">
-        <v>-23.06030610000001</v>
+        <v>-23.54295333</v>
       </c>
       <c r="Q72">
-        <v>-20.76030610000001</v>
+        <v>-21.24295333000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.5741788000810286</v>
+        <v>0.5923987587045125</v>
       </c>
       <c r="T72">
-        <v>2.596121699552548</v>
+        <v>2.685643137468153</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1111059935017134</v>
+        <v>0.109541120353802</v>
       </c>
       <c r="W72">
-        <v>0.209601206732296</v>
+        <v>0.2099702038205735</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3174456957191812</v>
+        <v>0.3129746295822914</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3208744847369158</v>
+        <v>0.3227744847369157</v>
       </c>
       <c r="C73">
-        <v>-25.7739178820388</v>
+        <v>-30.2747729324409</v>
       </c>
       <c r="D73">
-        <v>197.0680821179612</v>
+        <v>195.7162270675591</v>
       </c>
       <c r="E73">
-        <v>199.879</v>
+        <v>203.028</v>
       </c>
       <c r="F73">
-        <v>223.579</v>
+        <v>226.728</v>
       </c>
       <c r="G73">
         <v>0.737</v>
@@ -7273,37 +7273,37 @@
         <v>16.5</v>
       </c>
       <c r="M73">
-        <v>52.7199282</v>
+        <v>53.4624624</v>
       </c>
       <c r="N73">
-        <v>-36.2199282</v>
+        <v>-36.9624624</v>
       </c>
       <c r="O73">
-        <v>-12.67697487</v>
+        <v>-12.93686184</v>
       </c>
       <c r="P73">
-        <v>-23.54295333</v>
+        <v>-24.02560056</v>
       </c>
       <c r="Q73">
-        <v>-21.24295333</v>
+        <v>-21.72560056</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5923987587045123</v>
+        <v>0.6119201429439591</v>
       </c>
       <c r="T73">
-        <v>2.685643137468152</v>
+        <v>2.781558963806301</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.109541120353802</v>
+        <v>0.1080197159044436</v>
       </c>
       <c r="W73">
-        <v>0.2099702038205735</v>
+        <v>0.2103289509897322</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3129746295822914</v>
+        <v>0.3086277597269819</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3227744847369157</v>
+        <v>0.3246744847369157</v>
       </c>
       <c r="C74">
-        <v>-30.2747729324409</v>
+        <v>-34.75720733315046</v>
       </c>
       <c r="D74">
-        <v>195.7162270675591</v>
+        <v>194.3827926668495</v>
       </c>
       <c r="E74">
-        <v>203.028</v>
+        <v>206.177</v>
       </c>
       <c r="F74">
-        <v>226.728</v>
+        <v>229.877</v>
       </c>
       <c r="G74">
         <v>0.737</v>
@@ -7355,37 +7355,37 @@
         <v>16.5</v>
       </c>
       <c r="M74">
-        <v>53.4624624</v>
+        <v>54.2049966</v>
       </c>
       <c r="N74">
-        <v>-36.9624624</v>
+        <v>-37.7049966</v>
       </c>
       <c r="O74">
-        <v>-12.93686184</v>
+        <v>-13.19674881</v>
       </c>
       <c r="P74">
-        <v>-24.02560056</v>
+        <v>-24.50824779</v>
       </c>
       <c r="Q74">
-        <v>-21.72560056</v>
+        <v>-22.20824779</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6119201429439591</v>
+        <v>0.6328875556455872</v>
       </c>
       <c r="T74">
-        <v>2.781558963806301</v>
+        <v>2.884579666169496</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1080197159044436</v>
+        <v>0.1065399937687663</v>
       </c>
       <c r="W74">
-        <v>0.2103289509897322</v>
+        <v>0.2106778694693249</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3086277597269819</v>
+        <v>0.3043999821964752</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3246744847369157</v>
+        <v>0.3265744847369157</v>
       </c>
       <c r="C75">
-        <v>-34.75720733315046</v>
+        <v>-39.22159504159225</v>
       </c>
       <c r="D75">
-        <v>194.3827926668495</v>
+        <v>193.0674049584077</v>
       </c>
       <c r="E75">
-        <v>206.177</v>
+        <v>209.326</v>
       </c>
       <c r="F75">
-        <v>229.877</v>
+        <v>233.026</v>
       </c>
       <c r="G75">
         <v>0.737</v>
@@ -7437,37 +7437,37 @@
         <v>16.5</v>
       </c>
       <c r="M75">
-        <v>54.2049966</v>
+        <v>54.9475308</v>
       </c>
       <c r="N75">
-        <v>-37.7049966</v>
+        <v>-38.4475308</v>
       </c>
       <c r="O75">
-        <v>-13.19674881</v>
+        <v>-13.45663578</v>
       </c>
       <c r="P75">
-        <v>-24.50824779</v>
+        <v>-24.99089502</v>
       </c>
       <c r="Q75">
-        <v>-22.20824779</v>
+        <v>-22.69089502</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.6328875556455872</v>
+        <v>0.6554678462473407</v>
       </c>
       <c r="T75">
-        <v>2.884579666169496</v>
+        <v>2.995525037945247</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1065399937687663</v>
+        <v>0.1051002641232425</v>
       </c>
       <c r="W75">
-        <v>0.2106778694693249</v>
+        <v>0.2110173577197394</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3043999821964752</v>
+        <v>0.3002864689235499</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3265744847369157</v>
+        <v>0.3284744847369158</v>
       </c>
       <c r="C76">
-        <v>-39.22159504159225</v>
+        <v>-43.66829996095342</v>
       </c>
       <c r="D76">
-        <v>193.0674049584077</v>
+        <v>191.7697000390466</v>
       </c>
       <c r="E76">
-        <v>209.326</v>
+        <v>212.475</v>
       </c>
       <c r="F76">
-        <v>233.026</v>
+        <v>236.175</v>
       </c>
       <c r="G76">
         <v>0.737</v>
@@ -7519,37 +7519,37 @@
         <v>16.5</v>
       </c>
       <c r="M76">
-        <v>54.9475308</v>
+        <v>55.690065</v>
       </c>
       <c r="N76">
-        <v>-38.4475308</v>
+        <v>-39.190065</v>
       </c>
       <c r="O76">
-        <v>-13.45663578</v>
+        <v>-13.71652275</v>
       </c>
       <c r="P76">
-        <v>-24.99089502</v>
+        <v>-25.47354225</v>
       </c>
       <c r="Q76">
-        <v>-22.69089502</v>
+        <v>-23.17354225</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.6554678462473407</v>
+        <v>0.6798545600972343</v>
       </c>
       <c r="T76">
-        <v>2.995525037945247</v>
+        <v>3.115346039463057</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1051002641232425</v>
+        <v>0.1036989272682659</v>
       </c>
       <c r="W76">
-        <v>0.2110173577197394</v>
+        <v>0.2113477929501429</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3002864689235499</v>
+        <v>0.2962826493379026</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3284744847369158</v>
+        <v>0.3303744847369158</v>
       </c>
       <c r="C77">
-        <v>-43.66829996095342</v>
+        <v>-48.09767627582593</v>
       </c>
       <c r="D77">
-        <v>191.7697000390466</v>
+        <v>190.4893237241741</v>
       </c>
       <c r="E77">
-        <v>212.475</v>
+        <v>215.624</v>
       </c>
       <c r="F77">
-        <v>236.175</v>
+        <v>239.324</v>
       </c>
       <c r="G77">
         <v>0.737</v>
@@ -7601,37 +7601,37 @@
         <v>16.5</v>
       </c>
       <c r="M77">
-        <v>55.690065</v>
+        <v>56.4325992</v>
       </c>
       <c r="N77">
-        <v>-39.190065</v>
+        <v>-39.9325992</v>
       </c>
       <c r="O77">
-        <v>-13.71652275</v>
+        <v>-13.97640972</v>
       </c>
       <c r="P77">
-        <v>-25.47354225</v>
+        <v>-25.95618948</v>
       </c>
       <c r="Q77">
-        <v>-23.17354225</v>
+        <v>-23.65618948</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.6798545600972343</v>
+        <v>0.7062735001012858</v>
       </c>
       <c r="T77">
-        <v>3.115346039463057</v>
+        <v>3.245152124440684</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1036989272682659</v>
+        <v>0.1023344676989466</v>
       </c>
       <c r="W77">
-        <v>0.2113477929501429</v>
+        <v>0.2116695325165884</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2962826493379026</v>
+        <v>0.2923841934255618</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3303744847369158</v>
+        <v>0.3322744847369158</v>
       </c>
       <c r="C78">
-        <v>-48.09767627582593</v>
+        <v>-52.51006877449231</v>
       </c>
       <c r="D78">
-        <v>190.4893237241741</v>
+        <v>189.2259312255077</v>
       </c>
       <c r="E78">
-        <v>215.624</v>
+        <v>218.773</v>
       </c>
       <c r="F78">
-        <v>239.324</v>
+        <v>242.473</v>
       </c>
       <c r="G78">
         <v>0.737</v>
@@ -7683,37 +7683,37 @@
         <v>16.5</v>
       </c>
       <c r="M78">
-        <v>56.4325992</v>
+        <v>57.1751334</v>
       </c>
       <c r="N78">
-        <v>-39.9325992</v>
+        <v>-40.6751334</v>
       </c>
       <c r="O78">
-        <v>-13.97640972</v>
+        <v>-14.23629669</v>
       </c>
       <c r="P78">
-        <v>-25.95618948</v>
+        <v>-26.43883671</v>
       </c>
       <c r="Q78">
-        <v>-23.65618948</v>
+        <v>-24.13883671</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.7062735001012858</v>
+        <v>0.7349897392361243</v>
       </c>
       <c r="T78">
-        <v>3.245152124440684</v>
+        <v>3.38624569506854</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1023344676989466</v>
+        <v>0.1010054486379213</v>
       </c>
       <c r="W78">
-        <v>0.2116695325165884</v>
+        <v>0.2119829152111782</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2923841934255618</v>
+        <v>0.2885869961083466</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3322744847369158</v>
+        <v>0.3341744847369158</v>
       </c>
       <c r="C79">
-        <v>-52.51006877449231</v>
+        <v>-56.90581315847089</v>
       </c>
       <c r="D79">
-        <v>189.2259312255077</v>
+        <v>187.9791868415291</v>
       </c>
       <c r="E79">
-        <v>218.773</v>
+        <v>221.922</v>
       </c>
       <c r="F79">
-        <v>242.473</v>
+        <v>245.622</v>
       </c>
       <c r="G79">
         <v>0.737</v>
@@ -7765,37 +7765,37 @@
         <v>16.5</v>
       </c>
       <c r="M79">
-        <v>57.1751334</v>
+        <v>57.9176676</v>
       </c>
       <c r="N79">
-        <v>-40.6751334</v>
+        <v>-41.4176676</v>
       </c>
       <c r="O79">
-        <v>-14.23629669</v>
+        <v>-14.49618366</v>
       </c>
       <c r="P79">
-        <v>-26.43883671</v>
+        <v>-26.92148394</v>
       </c>
       <c r="Q79">
-        <v>-24.13883671</v>
+        <v>-24.62148394</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.7349897392361243</v>
+        <v>0.7663165455650391</v>
       </c>
       <c r="T79">
-        <v>3.38624569506854</v>
+        <v>3.540165953935293</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1010054486379213</v>
+        <v>0.0997105069887172</v>
       </c>
       <c r="W79">
-        <v>0.2119829152111782</v>
+        <v>0.2122882624520605</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2885869961083466</v>
+        <v>0.2848871628249063</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3341744847369158</v>
+        <v>0.3360744847369158</v>
       </c>
       <c r="C80">
-        <v>-56.90581315847089</v>
+        <v>-61.28523633990412</v>
       </c>
       <c r="D80">
-        <v>187.9791868415291</v>
+        <v>186.7487636600959</v>
       </c>
       <c r="E80">
-        <v>221.922</v>
+        <v>225.071</v>
       </c>
       <c r="F80">
-        <v>245.622</v>
+        <v>248.771</v>
       </c>
       <c r="G80">
         <v>0.737</v>
@@ -7847,37 +7847,37 @@
         <v>16.5</v>
       </c>
       <c r="M80">
-        <v>57.9176676</v>
+        <v>58.6602018</v>
       </c>
       <c r="N80">
-        <v>-41.4176676</v>
+        <v>-42.1602018</v>
       </c>
       <c r="O80">
-        <v>-14.49618366</v>
+        <v>-14.75607063</v>
       </c>
       <c r="P80">
-        <v>-26.92148394</v>
+        <v>-27.40413117</v>
       </c>
       <c r="Q80">
-        <v>-24.62148394</v>
+        <v>-25.10413117</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7663165455650391</v>
+        <v>0.8006268572586124</v>
       </c>
       <c r="T80">
-        <v>3.540165953935293</v>
+        <v>3.708745285075068</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0997105069887172</v>
+        <v>0.09844834867240433</v>
       </c>
       <c r="W80">
-        <v>0.2122882624520605</v>
+        <v>0.212585879383047</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2848871628249063</v>
+        <v>0.2812809962068695</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3360744847369158</v>
+        <v>0.3379744847369158</v>
       </c>
       <c r="C81">
-        <v>-61.28523633990412</v>
+        <v>-65.64865672734382</v>
       </c>
       <c r="D81">
-        <v>186.7487636600959</v>
+        <v>185.5343432726562</v>
       </c>
       <c r="E81">
-        <v>225.071</v>
+        <v>228.22</v>
       </c>
       <c r="F81">
-        <v>248.771</v>
+        <v>251.92</v>
       </c>
       <c r="G81">
         <v>0.737</v>
@@ -7929,37 +7929,37 @@
         <v>16.5</v>
       </c>
       <c r="M81">
-        <v>58.6602018</v>
+        <v>59.402736</v>
       </c>
       <c r="N81">
-        <v>-42.1602018</v>
+        <v>-42.902736</v>
       </c>
       <c r="O81">
-        <v>-14.75607063</v>
+        <v>-15.0159576</v>
       </c>
       <c r="P81">
-        <v>-27.40413117</v>
+        <v>-27.8867784</v>
       </c>
       <c r="Q81">
-        <v>-25.10413117</v>
+        <v>-25.5867784</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.8006268572586124</v>
+        <v>0.8383682001215431</v>
       </c>
       <c r="T81">
-        <v>3.708745285075068</v>
+        <v>3.894182549328822</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09844834867240433</v>
+        <v>0.09721774431399928</v>
       </c>
       <c r="W81">
-        <v>0.212585879383047</v>
+        <v>0.212876055890759</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2812809962068695</v>
+        <v>0.2777649837542836</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3379744847369158</v>
+        <v>0.3398744847369158</v>
       </c>
       <c r="C82">
-        <v>-65.64865672734382</v>
+        <v>-69.99638450045683</v>
       </c>
       <c r="D82">
-        <v>185.5343432726562</v>
+        <v>184.3356154995432</v>
       </c>
       <c r="E82">
-        <v>228.22</v>
+        <v>231.369</v>
       </c>
       <c r="F82">
-        <v>251.92</v>
+        <v>255.069</v>
       </c>
       <c r="G82">
         <v>0.737</v>
@@ -8011,37 +8011,37 @@
         <v>16.5</v>
       </c>
       <c r="M82">
-        <v>59.402736</v>
+        <v>60.1452702</v>
       </c>
       <c r="N82">
-        <v>-42.902736</v>
+        <v>-43.6452702</v>
       </c>
       <c r="O82">
-        <v>-15.0159576</v>
+        <v>-15.27584457</v>
       </c>
       <c r="P82">
-        <v>-27.8867784</v>
+        <v>-28.36942563</v>
       </c>
       <c r="Q82">
-        <v>-25.5867784</v>
+        <v>-26.06942563</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.8383682001215431</v>
+        <v>0.8800823159174138</v>
       </c>
       <c r="T82">
-        <v>3.894182549328822</v>
+        <v>4.099139525609286</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09721774431399928</v>
+        <v>0.09601752524839435</v>
       </c>
       <c r="W82">
-        <v>0.212876055890759</v>
+        <v>0.2131590675464286</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2777649837542836</v>
+        <v>0.2743357864239838</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3398744847369158</v>
+        <v>0.3417744847369158</v>
       </c>
       <c r="C83">
-        <v>-69.99638450045683</v>
+        <v>-74.32872187415126</v>
       </c>
       <c r="D83">
-        <v>184.3356154995432</v>
+        <v>183.1522781258488</v>
       </c>
       <c r="E83">
-        <v>231.369</v>
+        <v>234.518</v>
       </c>
       <c r="F83">
-        <v>255.069</v>
+        <v>258.218</v>
       </c>
       <c r="G83">
         <v>0.737</v>
@@ -8093,37 +8093,37 @@
         <v>16.5</v>
       </c>
       <c r="M83">
-        <v>60.1452702</v>
+        <v>60.88780440000001</v>
       </c>
       <c r="N83">
-        <v>-43.6452702</v>
+        <v>-44.38780440000001</v>
       </c>
       <c r="O83">
-        <v>-15.27584457</v>
+        <v>-15.53573154</v>
       </c>
       <c r="P83">
-        <v>-28.36942563</v>
+        <v>-28.85207286000001</v>
       </c>
       <c r="Q83">
-        <v>-26.06942563</v>
+        <v>-26.55207286000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8800823159174138</v>
+        <v>0.9264313334683814</v>
       </c>
       <c r="T83">
-        <v>4.099139525609286</v>
+        <v>4.326869499254247</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09601752524839435</v>
+        <v>0.09484657981853586</v>
       </c>
       <c r="W83">
-        <v>0.2131590675464286</v>
+        <v>0.2134351764787893</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2743357864239838</v>
+        <v>0.2709902280529596</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3417744847369158</v>
+        <v>0.3436744847369159</v>
       </c>
       <c r="C84">
-        <v>-74.32872187415126</v>
+        <v>-78.64596335259301</v>
       </c>
       <c r="D84">
-        <v>183.1522781258488</v>
+        <v>181.984036647407</v>
       </c>
       <c r="E84">
-        <v>234.518</v>
+        <v>237.667</v>
       </c>
       <c r="F84">
-        <v>258.218</v>
+        <v>261.367</v>
       </c>
       <c r="G84">
         <v>0.737</v>
@@ -8175,37 +8175,37 @@
         <v>16.5</v>
       </c>
       <c r="M84">
-        <v>60.88780440000001</v>
+        <v>61.63033860000001</v>
       </c>
       <c r="N84">
-        <v>-44.38780440000001</v>
+        <v>-45.13033860000001</v>
       </c>
       <c r="O84">
-        <v>-15.53573154</v>
+        <v>-15.79561851</v>
       </c>
       <c r="P84">
-        <v>-28.85207286000001</v>
+        <v>-29.33472009</v>
       </c>
       <c r="Q84">
-        <v>-26.55207286000001</v>
+        <v>-27.03472009000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.9264313334683814</v>
+        <v>0.9782331766135804</v>
       </c>
       <c r="T84">
-        <v>4.326869499254247</v>
+        <v>4.581391234504498</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09484657981853586</v>
+        <v>0.09370384994120409</v>
       </c>
       <c r="W84">
-        <v>0.2134351764787893</v>
+        <v>0.2137046321838641</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2709902280529596</v>
+        <v>0.2677252855462975</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3436744847369159</v>
+        <v>0.3455744847369158</v>
       </c>
       <c r="C85">
-        <v>-78.64596335259301</v>
+        <v>-82.94839597356307</v>
       </c>
       <c r="D85">
-        <v>181.984036647407</v>
+        <v>180.830604026437</v>
       </c>
       <c r="E85">
-        <v>237.667</v>
+        <v>240.816</v>
       </c>
       <c r="F85">
-        <v>261.367</v>
+        <v>264.516</v>
       </c>
       <c r="G85">
         <v>0.737</v>
@@ -8257,37 +8257,37 @@
         <v>16.5</v>
       </c>
       <c r="M85">
-        <v>61.63033860000001</v>
+        <v>62.37287280000001</v>
       </c>
       <c r="N85">
-        <v>-45.13033860000001</v>
+        <v>-45.87287280000001</v>
       </c>
       <c r="O85">
-        <v>-15.79561851</v>
+        <v>-16.05550548</v>
       </c>
       <c r="P85">
-        <v>-29.33472009</v>
+        <v>-29.81736732000001</v>
       </c>
       <c r="Q85">
-        <v>-27.03472009000001</v>
+        <v>-27.51736732000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.9782331766135804</v>
+        <v>1.036510250151929</v>
       </c>
       <c r="T85">
-        <v>4.581391234504498</v>
+        <v>4.867728186661028</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09370384994120409</v>
+        <v>0.09258832791809453</v>
       </c>
       <c r="W85">
-        <v>0.2137046321838641</v>
+        <v>0.2139676722769133</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2677252855462975</v>
+        <v>0.2645380797659844</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3455744847369158</v>
+        <v>0.3474744847369158</v>
       </c>
       <c r="C86">
-        <v>-82.94839597356301</v>
+        <v>-87.23629954358108</v>
       </c>
       <c r="D86">
-        <v>180.830604026437</v>
+        <v>179.6917004564189</v>
       </c>
       <c r="E86">
-        <v>240.816</v>
+        <v>243.965</v>
       </c>
       <c r="F86">
-        <v>264.516</v>
+        <v>267.665</v>
       </c>
       <c r="G86">
         <v>0.737</v>
@@ -8339,37 +8339,37 @@
         <v>16.5</v>
       </c>
       <c r="M86">
-        <v>62.3728728</v>
+        <v>63.11540699999999</v>
       </c>
       <c r="N86">
-        <v>-45.8728728</v>
+        <v>-46.61540699999999</v>
       </c>
       <c r="O86">
-        <v>-16.05550548</v>
+        <v>-16.31539245</v>
       </c>
       <c r="P86">
-        <v>-29.81736732</v>
+        <v>-30.30001454999999</v>
       </c>
       <c r="Q86">
-        <v>-27.51736732</v>
+        <v>-28.00001455</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.036510250151929</v>
+        <v>1.102557600162057</v>
       </c>
       <c r="T86">
-        <v>4.867728186661026</v>
+        <v>5.192243399105094</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09258832791809454</v>
+        <v>0.09149905347199934</v>
       </c>
       <c r="W86">
-        <v>0.2139676722769133</v>
+        <v>0.2142245231913026</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2645380797659844</v>
+        <v>0.2614258670628552</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3474744847369158</v>
+        <v>0.3493744847369158</v>
       </c>
       <c r="C87">
-        <v>-87.23629954358108</v>
+        <v>-91.50994686419855</v>
       </c>
       <c r="D87">
-        <v>179.6917004564189</v>
+        <v>178.5670531358014</v>
       </c>
       <c r="E87">
-        <v>243.965</v>
+        <v>247.114</v>
       </c>
       <c r="F87">
-        <v>267.665</v>
+        <v>270.814</v>
       </c>
       <c r="G87">
         <v>0.737</v>
@@ -8421,37 +8421,37 @@
         <v>16.5</v>
       </c>
       <c r="M87">
-        <v>63.11540699999999</v>
+        <v>63.85794119999999</v>
       </c>
       <c r="N87">
-        <v>-46.61540699999999</v>
+        <v>-47.35794119999999</v>
       </c>
       <c r="O87">
-        <v>-16.31539245</v>
+        <v>-16.57527942</v>
       </c>
       <c r="P87">
-        <v>-30.30001454999999</v>
+        <v>-30.78266177999999</v>
       </c>
       <c r="Q87">
-        <v>-28.00001455</v>
+        <v>-28.48266177999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.102557600162057</v>
+        <v>1.178040285887918</v>
       </c>
       <c r="T87">
-        <v>5.192243399105094</v>
+        <v>5.563117927612601</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09149905347199934</v>
+        <v>0.09043511098976677</v>
       </c>
       <c r="W87">
-        <v>0.2142245231913026</v>
+        <v>0.214475400828613</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2614258670628552</v>
+        <v>0.2583860313993337</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3493744847369158</v>
+        <v>0.3512744847369158</v>
       </c>
       <c r="C88">
-        <v>-91.50994686419855</v>
+        <v>-95.76960394984752</v>
       </c>
       <c r="D88">
-        <v>178.5670531358014</v>
+        <v>177.4563960501524</v>
       </c>
       <c r="E88">
-        <v>247.114</v>
+        <v>250.263</v>
       </c>
       <c r="F88">
-        <v>270.814</v>
+        <v>273.963</v>
       </c>
       <c r="G88">
         <v>0.737</v>
@@ -8503,37 +8503,37 @@
         <v>16.5</v>
       </c>
       <c r="M88">
-        <v>63.85794119999999</v>
+        <v>64.60047539999999</v>
       </c>
       <c r="N88">
-        <v>-47.35794119999999</v>
+        <v>-48.10047539999999</v>
       </c>
       <c r="O88">
-        <v>-16.57527942</v>
+        <v>-16.83516639</v>
       </c>
       <c r="P88">
-        <v>-30.78266177999999</v>
+        <v>-31.26530901</v>
       </c>
       <c r="Q88">
-        <v>-28.48266177999999</v>
+        <v>-28.96530901</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.178040285887918</v>
+        <v>1.265135692494681</v>
       </c>
       <c r="T88">
-        <v>5.563117927612601</v>
+        <v>5.991050075890493</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09043511098976677</v>
+        <v>0.08939562695540164</v>
       </c>
       <c r="W88">
-        <v>0.214475400828613</v>
+        <v>0.2147205111639163</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2583860313993337</v>
+        <v>0.2554160770154332</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3512744847369158</v>
+        <v>0.3531744847369158</v>
       </c>
       <c r="C89">
-        <v>-95.76960394984752</v>
+        <v>-100.0155302376097</v>
       </c>
       <c r="D89">
-        <v>177.4563960501524</v>
+        <v>176.3594697623903</v>
       </c>
       <c r="E89">
-        <v>250.263</v>
+        <v>253.412</v>
       </c>
       <c r="F89">
-        <v>273.963</v>
+        <v>277.112</v>
       </c>
       <c r="G89">
         <v>0.737</v>
@@ -8585,37 +8585,37 @@
         <v>16.5</v>
       </c>
       <c r="M89">
-        <v>64.60047539999999</v>
+        <v>65.34300959999999</v>
       </c>
       <c r="N89">
-        <v>-48.10047539999999</v>
+        <v>-48.84300959999999</v>
       </c>
       <c r="O89">
-        <v>-16.83516639</v>
+        <v>-17.09505335999999</v>
       </c>
       <c r="P89">
-        <v>-31.26530901</v>
+        <v>-31.74795623999999</v>
       </c>
       <c r="Q89">
-        <v>-28.96530901</v>
+        <v>-29.44795624</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.265135692494681</v>
+        <v>1.366747000202572</v>
       </c>
       <c r="T89">
-        <v>5.991050075890493</v>
+        <v>6.490304248881368</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08939562695540164</v>
+        <v>0.08837976755818117</v>
       </c>
       <c r="W89">
-        <v>0.2147205111639163</v>
+        <v>0.2149600508097809</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2554160770154332</v>
+        <v>0.2525136215948034</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3531744847369158</v>
+        <v>0.3550744847369158</v>
       </c>
       <c r="C90">
-        <v>-100.0155302376097</v>
+        <v>-104.2479787892534</v>
       </c>
       <c r="D90">
-        <v>176.3594697623903</v>
+        <v>175.2760212107466</v>
       </c>
       <c r="E90">
-        <v>253.412</v>
+        <v>256.561</v>
       </c>
       <c r="F90">
-        <v>277.112</v>
+        <v>280.261</v>
       </c>
       <c r="G90">
         <v>0.737</v>
@@ -8667,37 +8667,37 @@
         <v>16.5</v>
       </c>
       <c r="M90">
-        <v>65.34300959999999</v>
+        <v>66.0855438</v>
       </c>
       <c r="N90">
-        <v>-48.84300959999999</v>
+        <v>-49.5855438</v>
       </c>
       <c r="O90">
-        <v>-17.09505335999999</v>
+        <v>-17.35494033</v>
       </c>
       <c r="P90">
-        <v>-31.74795623999999</v>
+        <v>-32.23060347</v>
       </c>
       <c r="Q90">
-        <v>-29.44795624</v>
+        <v>-29.93060347</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.366747000202572</v>
+        <v>1.486833091130078</v>
       </c>
       <c r="T90">
-        <v>6.490304248881368</v>
+        <v>7.080331907870585</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08837976755818117</v>
+        <v>0.08738673646202182</v>
       </c>
       <c r="W90">
-        <v>0.2149600508097809</v>
+        <v>0.2151942075422553</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2525136215948034</v>
+        <v>0.2496763898914909</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3550744847369158</v>
+        <v>0.3569744847369157</v>
       </c>
       <c r="C91">
-        <v>-104.2479787892534</v>
+        <v>-108.4671964858681</v>
       </c>
       <c r="D91">
-        <v>175.2760212107466</v>
+        <v>174.2058035141319</v>
       </c>
       <c r="E91">
-        <v>256.561</v>
+        <v>259.71</v>
       </c>
       <c r="F91">
-        <v>280.261</v>
+        <v>283.41</v>
       </c>
       <c r="G91">
         <v>0.737</v>
@@ -8749,37 +8749,37 @@
         <v>16.5</v>
       </c>
       <c r="M91">
-        <v>66.0855438</v>
+        <v>66.82807799999999</v>
       </c>
       <c r="N91">
-        <v>-49.5855438</v>
+        <v>-50.32807799999999</v>
       </c>
       <c r="O91">
-        <v>-17.35494033</v>
+        <v>-17.61482729999999</v>
       </c>
       <c r="P91">
-        <v>-32.23060347</v>
+        <v>-32.7132507</v>
       </c>
       <c r="Q91">
-        <v>-29.93060347</v>
+        <v>-30.4132507</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.486833091130078</v>
+        <v>1.630936400243086</v>
       </c>
       <c r="T91">
-        <v>7.080331907870585</v>
+        <v>7.788365098657642</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08738673646202182</v>
+        <v>0.08641577272355493</v>
       </c>
       <c r="W91">
-        <v>0.2151942075422553</v>
+        <v>0.2154231607917858</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2496763898914909</v>
+        <v>0.2469022077815854</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3569744847369157</v>
+        <v>0.3588744847369157</v>
       </c>
       <c r="C92">
-        <v>-108.4671964858681</v>
+        <v>-112.673424215413</v>
       </c>
       <c r="D92">
-        <v>174.2058035141319</v>
+        <v>173.148575784587</v>
       </c>
       <c r="E92">
-        <v>259.71</v>
+        <v>262.859</v>
       </c>
       <c r="F92">
-        <v>283.41</v>
+        <v>286.559</v>
       </c>
       <c r="G92">
         <v>0.737</v>
@@ -8831,37 +8831,37 @@
         <v>16.5</v>
       </c>
       <c r="M92">
-        <v>66.82807799999999</v>
+        <v>67.5706122</v>
       </c>
       <c r="N92">
-        <v>-50.32807799999999</v>
+        <v>-51.0706122</v>
       </c>
       <c r="O92">
-        <v>-17.61482729999999</v>
+        <v>-17.87471427</v>
       </c>
       <c r="P92">
-        <v>-32.7132507</v>
+        <v>-33.19589793</v>
       </c>
       <c r="Q92">
-        <v>-30.4132507</v>
+        <v>-30.89589793</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.630936400243086</v>
+        <v>1.807062666936762</v>
       </c>
       <c r="T92">
-        <v>7.788365098657642</v>
+        <v>8.653738998508492</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08641577272355493</v>
+        <v>0.08546614884747189</v>
       </c>
       <c r="W92">
-        <v>0.2154231607917858</v>
+        <v>0.2156470821017661</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2469022077815854</v>
+        <v>0.2441889967070625</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3588744847369157</v>
+        <v>0.3607744847369158</v>
       </c>
       <c r="C93">
-        <v>-112.673424215413</v>
+        <v>-116.8668970534764</v>
       </c>
       <c r="D93">
-        <v>173.148575784587</v>
+        <v>172.1041029465236</v>
       </c>
       <c r="E93">
-        <v>262.859</v>
+        <v>266.008</v>
       </c>
       <c r="F93">
-        <v>286.559</v>
+        <v>289.708</v>
       </c>
       <c r="G93">
         <v>0.737</v>
@@ -8913,37 +8913,37 @@
         <v>16.5</v>
       </c>
       <c r="M93">
-        <v>67.5706122</v>
+        <v>68.31314639999999</v>
       </c>
       <c r="N93">
-        <v>-51.0706122</v>
+        <v>-51.81314639999999</v>
       </c>
       <c r="O93">
-        <v>-17.87471427</v>
+        <v>-18.13460123999999</v>
       </c>
       <c r="P93">
-        <v>-33.19589793</v>
+        <v>-33.67854516</v>
       </c>
       <c r="Q93">
-        <v>-30.89589793</v>
+        <v>-31.37854516</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.807062666936762</v>
+        <v>2.027220500303859</v>
       </c>
       <c r="T93">
-        <v>8.653738998508492</v>
+        <v>9.735456373322059</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08546614884747189</v>
+        <v>0.08453716896869502</v>
       </c>
       <c r="W93">
-        <v>0.2156470821017661</v>
+        <v>0.2158661355571817</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2441889967070625</v>
+        <v>0.2415347684819859</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3607744847369158</v>
+        <v>0.3626744847369158</v>
       </c>
       <c r="C94">
-        <v>-116.8668970534764</v>
+        <v>-121.0478444375325</v>
       </c>
       <c r="D94">
-        <v>172.1041029465236</v>
+        <v>171.0721555624674</v>
       </c>
       <c r="E94">
-        <v>266.008</v>
+        <v>269.157</v>
       </c>
       <c r="F94">
-        <v>289.708</v>
+        <v>292.857</v>
       </c>
       <c r="G94">
         <v>0.737</v>
@@ -8995,37 +8995,37 @@
         <v>16.5</v>
       </c>
       <c r="M94">
-        <v>68.31314639999999</v>
+        <v>69.0556806</v>
       </c>
       <c r="N94">
-        <v>-51.81314639999999</v>
+        <v>-52.5556806</v>
       </c>
       <c r="O94">
-        <v>-18.13460123999999</v>
+        <v>-18.39448821</v>
       </c>
       <c r="P94">
-        <v>-33.67854516</v>
+        <v>-34.16119239</v>
       </c>
       <c r="Q94">
-        <v>-31.37854516</v>
+        <v>-31.86119239000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.027220500303859</v>
+        <v>2.310280571775839</v>
       </c>
       <c r="T94">
-        <v>9.735456373322059</v>
+        <v>11.12623585522521</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08453716896869502</v>
+        <v>0.08362816715182733</v>
       </c>
       <c r="W94">
-        <v>0.2158661355571817</v>
+        <v>0.2160804781855991</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2415347684819859</v>
+        <v>0.2389376204337924</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3626744847369158</v>
+        <v>0.3645744847369158</v>
       </c>
       <c r="C95">
-        <v>-121.0478444375325</v>
+        <v>-125.2164903349667</v>
       </c>
       <c r="D95">
-        <v>171.0721555624674</v>
+        <v>170.0525096650333</v>
       </c>
       <c r="E95">
-        <v>269.157</v>
+        <v>272.306</v>
       </c>
       <c r="F95">
-        <v>292.857</v>
+        <v>296.006</v>
       </c>
       <c r="G95">
         <v>0.737</v>
@@ -9077,37 +9077,37 @@
         <v>16.5</v>
       </c>
       <c r="M95">
-        <v>69.0556806</v>
+        <v>69.7982148</v>
       </c>
       <c r="N95">
-        <v>-52.5556806</v>
+        <v>-53.2982148</v>
       </c>
       <c r="O95">
-        <v>-18.39448821</v>
+        <v>-18.65437518</v>
       </c>
       <c r="P95">
-        <v>-34.16119239</v>
+        <v>-34.64383961999999</v>
       </c>
       <c r="Q95">
-        <v>-31.86119239000001</v>
+        <v>-32.34383962</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.310280571775839</v>
+        <v>2.687694000405145</v>
       </c>
       <c r="T95">
-        <v>11.12623585522521</v>
+        <v>12.98060849776275</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08362816715182733</v>
+        <v>0.08273850579914832</v>
       </c>
       <c r="W95">
-        <v>0.2160804781855991</v>
+        <v>0.2162902603325608</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2389376204337924</v>
+        <v>0.2363957308547094</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3645744847369158</v>
+        <v>0.3664744847369158</v>
       </c>
       <c r="C96">
-        <v>-125.2164903349667</v>
+        <v>-129.3730534051269</v>
       </c>
       <c r="D96">
-        <v>170.0525096650333</v>
+        <v>169.0449465948731</v>
       </c>
       <c r="E96">
-        <v>272.306</v>
+        <v>275.455</v>
       </c>
       <c r="F96">
-        <v>296.006</v>
+        <v>299.155</v>
       </c>
       <c r="G96">
         <v>0.737</v>
@@ -9159,37 +9159,37 @@
         <v>16.5</v>
       </c>
       <c r="M96">
-        <v>69.7982148</v>
+        <v>70.54074899999999</v>
       </c>
       <c r="N96">
-        <v>-53.2982148</v>
+        <v>-54.04074899999999</v>
       </c>
       <c r="O96">
-        <v>-18.65437518</v>
+        <v>-18.91426215</v>
       </c>
       <c r="P96">
-        <v>-34.64383961999999</v>
+        <v>-35.12648684999999</v>
       </c>
       <c r="Q96">
-        <v>-32.34383962</v>
+        <v>-32.82648684999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.687694000405145</v>
+        <v>3.216072800486176</v>
       </c>
       <c r="T96">
-        <v>12.98060849776275</v>
+        <v>15.5767301973153</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08273850579914832</v>
+        <v>0.08186757415915728</v>
       </c>
       <c r="W96">
-        <v>0.2162902603325608</v>
+        <v>0.2164956260132707</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2363957308547094</v>
+        <v>0.2339073547404494</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3664744847369158</v>
+        <v>0.3683744847369158</v>
       </c>
       <c r="C97">
-        <v>-129.3730534051269</v>
+        <v>-133.5177471556485</v>
       </c>
       <c r="D97">
-        <v>169.0449465948731</v>
+        <v>168.0492528443515</v>
       </c>
       <c r="E97">
-        <v>275.455</v>
+        <v>278.604</v>
       </c>
       <c r="F97">
-        <v>299.155</v>
+        <v>302.304</v>
       </c>
       <c r="G97">
         <v>0.737</v>
@@ -9241,37 +9241,37 @@
         <v>16.5</v>
       </c>
       <c r="M97">
-        <v>70.54074899999999</v>
+        <v>71.2832832</v>
       </c>
       <c r="N97">
-        <v>-54.04074899999999</v>
+        <v>-54.7832832</v>
       </c>
       <c r="O97">
-        <v>-18.91426215</v>
+        <v>-19.17414912</v>
       </c>
       <c r="P97">
-        <v>-35.12648684999999</v>
+        <v>-35.60913408</v>
       </c>
       <c r="Q97">
-        <v>-32.82648684999999</v>
+        <v>-33.30913408000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.216072800486176</v>
+        <v>4.008641000607723</v>
       </c>
       <c r="T97">
-        <v>15.5767301973153</v>
+        <v>19.47091274664414</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08186757415915728</v>
+        <v>0.08101478692833272</v>
       </c>
       <c r="W97">
-        <v>0.2164956260132707</v>
+        <v>0.2166967132422991</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2339073547404494</v>
+        <v>0.2314708197952363</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3683744847369158</v>
+        <v>0.3702744847369158</v>
       </c>
       <c r="C98">
-        <v>-133.5177471556484</v>
+        <v>-137.6507800932865</v>
       </c>
       <c r="D98">
-        <v>168.0492528443516</v>
+        <v>167.0652199067135</v>
       </c>
       <c r="E98">
-        <v>278.604</v>
+        <v>281.753</v>
       </c>
       <c r="F98">
-        <v>302.304</v>
+        <v>305.453</v>
       </c>
       <c r="G98">
         <v>0.737</v>
@@ -9323,37 +9323,37 @@
         <v>16.5</v>
       </c>
       <c r="M98">
-        <v>71.2832832</v>
+        <v>72.02581739999999</v>
       </c>
       <c r="N98">
-        <v>-54.7832832</v>
+        <v>-55.52581739999999</v>
       </c>
       <c r="O98">
-        <v>-19.17414912</v>
+        <v>-19.43403609</v>
       </c>
       <c r="P98">
-        <v>-35.60913408</v>
+        <v>-36.09178131</v>
       </c>
       <c r="Q98">
-        <v>-33.30913408000001</v>
+        <v>-33.79178131</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.008641000607711</v>
+        <v>5.329588000810282</v>
       </c>
       <c r="T98">
-        <v>19.47091274664409</v>
+        <v>25.96121699552545</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08101478692833272</v>
+        <v>0.08017958293938085</v>
       </c>
       <c r="W98">
-        <v>0.2166967132422991</v>
+        <v>0.216893654342894</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2314708197952363</v>
+        <v>0.2290845226839453</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3702744847369158</v>
+        <v>0.3721744847369158</v>
       </c>
       <c r="C99">
-        <v>-137.6507800932865</v>
+        <v>-141.77235586948</v>
       </c>
       <c r="D99">
-        <v>167.0652199067135</v>
+        <v>166.09264413052</v>
       </c>
       <c r="E99">
-        <v>281.753</v>
+        <v>284.902</v>
       </c>
       <c r="F99">
-        <v>305.453</v>
+        <v>308.602</v>
       </c>
       <c r="G99">
         <v>0.737</v>
@@ -9405,37 +9405,37 @@
         <v>16.5</v>
       </c>
       <c r="M99">
-        <v>72.02581739999999</v>
+        <v>72.7683516</v>
       </c>
       <c r="N99">
-        <v>-55.52581739999999</v>
+        <v>-56.2683516</v>
       </c>
       <c r="O99">
-        <v>-19.43403609</v>
+        <v>-19.69392306</v>
       </c>
       <c r="P99">
-        <v>-36.09178131</v>
+        <v>-36.57442854</v>
       </c>
       <c r="Q99">
-        <v>-33.79178131</v>
+        <v>-34.27442854</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.329588000810282</v>
+        <v>7.971482001215423</v>
       </c>
       <c r="T99">
-        <v>25.96121699552545</v>
+        <v>38.94182549328818</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08017958293938085</v>
+        <v>0.07936142392979532</v>
       </c>
       <c r="W99">
-        <v>0.216893654342894</v>
+        <v>0.2170865762373543</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2290845226839453</v>
+        <v>0.2267469255137009</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3721744847369158</v>
+        <v>0.3740744847369157</v>
       </c>
       <c r="C100">
-        <v>-141.77235586948</v>
+        <v>-145.8826734208605</v>
       </c>
       <c r="D100">
-        <v>166.09264413052</v>
+        <v>165.1313265791395</v>
       </c>
       <c r="E100">
-        <v>284.902</v>
+        <v>288.051</v>
       </c>
       <c r="F100">
-        <v>308.602</v>
+        <v>311.751</v>
       </c>
       <c r="G100">
         <v>0.737</v>
@@ -9487,37 +9487,37 @@
         <v>16.5</v>
       </c>
       <c r="M100">
-        <v>72.7683516</v>
+        <v>73.5108858</v>
       </c>
       <c r="N100">
-        <v>-56.2683516</v>
+        <v>-57.0108858</v>
       </c>
       <c r="O100">
-        <v>-19.69392306</v>
+        <v>-19.95381003</v>
       </c>
       <c r="P100">
-        <v>-36.57442854</v>
+        <v>-37.05707577</v>
       </c>
       <c r="Q100">
-        <v>-34.27442854</v>
+        <v>-34.75707577</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>7.971482001215423</v>
+        <v>15.89716400243084</v>
       </c>
       <c r="T100">
-        <v>38.94182549328818</v>
+        <v>77.88365098657634</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07936142392979532</v>
+        <v>0.07855979338504993</v>
       </c>
       <c r="W100">
-        <v>0.2170865762373543</v>
+        <v>0.2172756007198052</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2267469255137009</v>
+        <v>0.2244565525287141</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3740744847369157</v>
-      </c>
-      <c r="C101">
-        <v>-145.8826734208605</v>
-      </c>
-      <c r="D101">
-        <v>165.1313265791395</v>
-      </c>
-      <c r="E101">
-        <v>288.051</v>
-      </c>
-      <c r="F101">
-        <v>311.751</v>
-      </c>
-      <c r="G101">
-        <v>0.737</v>
-      </c>
-      <c r="H101">
-        <v>291.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>18.8</v>
-      </c>
-      <c r="K101">
-        <v>2.299999999999999</v>
-      </c>
-      <c r="L101">
-        <v>16.5</v>
-      </c>
-      <c r="M101">
-        <v>73.5108858</v>
-      </c>
-      <c r="N101">
-        <v>-57.0108858</v>
-      </c>
-      <c r="O101">
-        <v>-19.95381003</v>
-      </c>
-      <c r="P101">
-        <v>-37.05707577</v>
-      </c>
-      <c r="Q101">
-        <v>-34.75707577</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>15.89716400243084</v>
-      </c>
-      <c r="T101">
-        <v>77.88365098657634</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07855979338504993</v>
-      </c>
-      <c r="W101">
-        <v>0.2172756007198052</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2244565525287141</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
